--- a/tempFiles/testcases.xlsx
+++ b/tempFiles/testcases.xlsx
@@ -424,14 +424,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L89"/>
+  <dimension ref="A1:L85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" outlineLevel="1" width="13" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col hidden="1" outlineLevel="1" width="13" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
     <col hidden="1" outlineLevel="1" width="13" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
@@ -1252,7 +1252,7 @@
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx
-2. 账户中拥有50ETFM2504C2400 空仓3手，50ETFM2504C2500 多仓5手，50ETFM2504C2600 空仓3手，50ETFM2504C2700 多仓5手，50ETFM2504C2800 空仓3手</t>
+2. 账户中拥有50ETFM2504C2400、C2600、C2800 空仓各1手，C2500、C2700 多仓各1手</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       <c r="E15" s="2" t="inlineStr">
         <is>
           <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx
-2. 账户中拥有50ETFM2504P2400 空仓3手，50ETFM2504P2500 多仓5手，50ETFM2504P2600 空仓3手，50ETFM2504P2700 多仓5手，50ETFM2504P2800 空仓3手</t>
+2. 账户中拥有50ETFM2504P2400、P2600、P2800 空仓各1手，50ETFM2504P2500、P2700 多仓各1手</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1386,7 +1386,7 @@
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx
-2. 账户中拥有50ETFM2504C2400 空仓3手，50ETFM2504C2500 多仓5手，50ETFM2504C2600 空仓3手，50ETFM2504C2700 多仓5手，50ETFM2504C2800 空仓3手</t>
+2. 账户中拥有50ETFM2504C2400、C2600、C2800 空仓各1手，C2500、C2700 多仓各1手</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1453,7 +1453,7 @@
       <c r="E17" s="2" t="inlineStr">
         <is>
           <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx
-2. 账户中拥有50ETFM2504P2400 空仓3手，50ETFM2504P2500 多仓5手，50ETFM2504P2600 空仓3手，50ETFM2504P2700 多仓5手，50ETFM2504P2800 空仓3手</t>
+2. 账户中拥有50ETFM2504P2400、P2600、P2800 空仓各1手，50ETFM2504P2500、P2700 多仓各1手</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1520,7 +1520,7 @@
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx
-2. 账户中拥有50ETFM2504P2400 空仓3手，50ETFM2504C2400 空仓3手，50ETFM2504P2600 空仓3手，50ETFM2504C2700 空仓3手，50ETFM2504P2800 空仓3手</t>
+2. 账户中拥有50ETFM2504P2400、P2600、C2400、C2700、C2800 空仓各1手</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1585,7 +1585,7 @@
       <c r="E19" s="2" t="inlineStr">
         <is>
           <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx
-2. 账户中拥有50ETFM2504P2400 空仓3手，50ETFM2504C2400 空仓3手，50ETFM2504P2600 空仓3手，50ETFM2504C2700 空仓3手，50ETFM2504P2800 空仓3手</t>
+2. 账户中拥有50ETFM2504P2400、P2600、C2400、C2700、C2800 空仓各1手</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1705,7 +1705,7 @@
       <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>大商所期权&gt;组合类型：卖出跨式</t>
+          <t>大商所期权&gt;组合类型：期权日历价差</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1717,7 +1717,7 @@
       <c r="E21" s="2" t="inlineStr">
         <is>
           <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx
-2. 账户中拥有A2507C4000、P3800、P4000、P4200空仓，各1手</t>
+2. 账户中拥有B2507C4000、P4000  多仓各1手；B2509C4000、P4000空仓，各1手</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1726,136 +1726,6 @@
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>1. 当前处于期权组合的界面
-2. 点击下拉“标的品种”
-3. 尝试下拉组合类型
-4. 下拉合约1
-5. 选择C4000持仓
-6. 下拉合约2</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>1. _
-2. 下拉只有豆一持仓，选择豆一
-3. 选择【卖出跨式】；卖出C1、P1；C1 = P1
-4. 左腿合约展示C4000  空，没有看跌P持仓，没有多仓
-5. _
-6. 由于C1=P1，合约2在现有持仓中只能有一个下拉选项，P4000  空</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>大商所期权&gt;组合类型：卖出宽跨式</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx
-2. 账户中拥有A2507C4000、P3800、P4000、P4200空仓，各1手</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>1. 当前处于期权组合的界面
-2. 点击下拉“标的品种”
-3. 尝试下拉组合类型
-4. 下拉合约1
-5. 选择C4000持仓
-6. 下拉合约2</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1. _
-2. 下拉只有豆一持仓，选择豆一
-3. 选择【卖出宽跨式】；卖出C1、P1；C1 &gt; P1
-4. 左腿合约展示C4000  空，没有看跌P持仓，没有多仓
-5. _
-6. 由于C1&gt;P1，合约2在现有持仓中只能有一个下拉选项，P3800  空</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr"/>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>大商所期权&gt;组合类型：买入垂直价差</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr"/>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx
-2. 账户中拥有B2507C4000、P4000  多仓各1手；C3800、P4200空仓，各1手</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1. 当前处于期权组合的界面
 2. 点击下拉“标的品种”
@@ -1866,63 +1736,63 @@
 7. 更改合约1为P4000持仓，重新下拉合约2</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>1. _
 2. 下拉只有豆二持仓，选择豆二
-3. 选择【买入垂直价差】；买入C1，卖出C2；C1&gt;C2；或者：买入P1，卖出P2；P1&lt;P2；
+3. 选择【期权日历价差】；买入远月C1，卖出近月C1；或者买入远月P1，卖出近月P1；
 4. 左腿合约展示A2507C4000、P4000   只有多仓
 5. _
-6. 由于C1&gt;C2，合约2在现有持仓中只能有一个下拉选项，C3800  空
-7. 由于P1&lt;P2，合约2在现有持仓中只能有一个下拉选项，P4200  空</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
+6. 买入远月C1，卖出近月C1，合约2在现有持仓中只能有一个下拉选项，A2509C4000  空
+7. 合约2在现有持仓中只能有一个下拉选项，A2509P4000  空</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr"/>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>大商所期权&gt;组合类型：卖出垂直价差</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>大商所期权&gt;组合类型：买入垂直价差</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx
-2. 账户中拥有B2507C4000、P4000  多仓各1手；C4200、P3800空仓，各1手</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+2. 账户中拥有B2507C4000、P4000  多仓各1手；C3800、P4200空仓，各1手</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>1. 当前处于期权组合的界面
 2. 点击下拉“标的品种”
@@ -1933,63 +1803,63 @@
 7. 更改合约1为P4000持仓，重新下拉合约2</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>1. _
 2. 下拉只有豆二持仓，选择豆二
-3. 选择【卖出垂直价差】；买入C1，卖出C2；C1&lt;C2；或者：买入P1，卖出P2；P1&gt;P2；
+3. 选择【买入垂直价差】；买入C1，卖出C2；C1&gt;C2；或者：买入P1，卖出P2；P1&lt;P2；
 4. 左腿合约展示A2507C4000、P4000   只有多仓
 5. _
-6. 由于C1&lt;C2，合约2在现有持仓中只能有一个下拉选项，C4200  空
-7. 由于P1&gt;P2，合约2在现有持仓中只能有一个下拉选项，P3800  空</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+6. 由于C1&gt;C2，合约2在现有持仓中只能有一个下拉选项，C3800  空
+7. 由于P1&lt;P2，合约2在现有持仓中只能有一个下拉选项，P4200  空</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>大商所期权&gt;组合类型：期权日历价差</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr"/>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>大商所期权&gt;组合类型：卖出垂直价差</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx
-2. 账户中拥有B2507C4000、P4000  多仓各1手；B2509C4000、P4000空仓，各1手</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+2. 账户中拥有B2507C4000、P4000  多仓各1手；C4200、P3800空仓，各1手</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1. 当前处于期权组合的界面
 2. 点击下拉“标的品种”
@@ -2000,15 +1870,145 @@
 7. 更改合约1为P4000持仓，重新下拉合约2</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>1. _
 2. 下拉只有豆二持仓，选择豆二
-3. 选择【期权日历价差】；买入远月C1，卖出近月C1；或者买入远月P1，卖出近月P1；
+3. 选择【卖出垂直价差】；买入C1，卖出C2；C1&lt;C2；或者：买入P1，卖出P2；P1&gt;P2；
 4. 左腿合约展示A2507C4000、P4000   只有多仓
 5. _
-6. 买入远月C1，卖出近月C1，合约2在现有持仓中只能有一个下拉选项，A2509C4000  空
-7. 合约2在现有持仓中只能有一个下拉选项，A2509P4000  空</t>
+6. 由于C1&lt;C2，合约2在现有持仓中只能有一个下拉选项，C4200  空
+7. 由于P1&gt;P2，合约2在现有持仓中只能有一个下拉选项，P3800  空</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>大商所期权&gt;组合类型：卖出跨式</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx
+2. 账户中拥有A2507C4000、P3800、P4000、P4200空仓，各1手</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于期权组合的界面
+2. 点击下拉“标的品种”
+3. 尝试下拉组合类型
+4. 下拉合约1
+5. 选择C4000持仓
+6. 下拉合约2</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 下拉只有豆一持仓，选择豆一
+3. 选择【卖出跨式】；卖出C1、P1；C1 = P1
+4. 左腿合约展示C4000  空，没有看跌P持仓，没有多仓
+5. _
+6. 由于C1=P1，合约2在现有持仓中只能有一个下拉选项，P4000  空</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>大商所期权&gt;组合类型：卖出宽跨式</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr"/>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx
+2. 账户中拥有A2507C4000、P3800、P4000、P4200空仓，各1手</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于期权组合的界面
+2. 点击下拉“标的品种”
+3. 尝试下拉组合类型
+4. 下拉合约1
+5. 选择C4000持仓
+6. 下拉合约2</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 下拉只有豆一持仓，选择豆一
+3. 选择【卖出宽跨式】；卖出C1、P1；C1 &gt; P1
+4. 左腿合约展示C4000  空，没有看跌P持仓，没有多仓
+5. _
+6. 由于C1&gt;P1，合约2在现有持仓中只能有一个下拉选项，P3800  空</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2047,7 +2047,8 @@
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
+          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx
+2. 账户中拥有50ETFM2504P2400、P2600、P2800 空仓各3手，50ETFM2504P2500、P2700 多仓各3手</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2105,7 +2106,8 @@
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
+          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx
+2. 账户中拥有50ETFM2504P2400、P2600、P2800 空仓各3手，50ETFM2504P2500、P2700 多仓各3手</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -2281,7 +2283,8 @@
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
+          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx
+2. 账户中拥有50ETFM2504P2400、P2600、P2800 空仓各3手，50ETFM2504P2500、P2700 多仓各3手</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2295,16 +2298,18 @@
 2. 委托数量输入2手
 3. 点击【申请组合】
 4. 点击【取消】
-5. 重复步骤3，点击【确定】</t>
+5. 重复步骤3，点击【确定】
+6. 退出界面，进入交易相关 - 交易日志</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>1. 该测试场景可用为3手
 2. _
-3. 弹出发单弹框提示，内容2手组合申请
+3. 弹出发单弹框提示，内容标题为【确认下单】展示合约1、合约2、组合类型、方向、手数
 4. 弹框关闭无事发生
-5. 成功组合，底下组合持仓列表多一笔持仓，组合委托列表多一条成功记录；可组更新为1，可拆更新为2</t>
+5. 成功组合，底下组合持仓列表多一笔持仓，组合委托列表多一条成功记录；可组更新为1，可拆更新为2
+6. 交易日志中也展示  展示合约1、合约2、组合类型、方向、手数</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2343,7 +2348,8 @@
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
+          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx
+2. 账户中拥有50ETFM2504P2400、P2600、P2800 空仓各3手，50ETFM2504P2500、P2700 多仓各3手</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2407,7 +2413,8 @@
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
+          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx
+2. 账户中拥有50ETFM2504P2400、P2600、P2800 空仓各3手，50ETFM2504P2500、P2700 多仓各3手</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2469,7 +2476,8 @@
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
+          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx
+2. 账户中拥有50ETFM2504P2400、P2600、P2800 空仓各3手，50ETFM2504P2500、P2700 多仓各3手</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2589,7 +2597,8 @@
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
+          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx
+2. 账户中拥有50ETFM2504P2400、P2600、P2800 空仓各3手，50ETFM2504P2500、P2700 多仓各3手</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2638,7 +2647,7 @@
       <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>期权组合&gt;字段：组合保证金、拆分后保证金</t>
+          <t>期权组合&gt;跨设备字段刷新</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2649,7 +2658,8 @@
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
+          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx
+2. 账户中拥有50ETFM2504P2400、P2600、P2800 空仓各3手，50ETFM2504P2500、P2700 多仓各3手</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2660,13 +2670,19 @@
       <c r="G36" s="2" t="inlineStr">
         <is>
           <t>1. 当前使用ETF期权  看涨牛市测试背景，事先已组合2手，当前可组1手，可拆2手
-2. 查看此条记录的组合保证金、拆分后保证金字段数值</t>
+2. 查看此条记录的总仓、可拆字段数值
+3. A设置呆在此界面，再次新开一个B设备进入此界面
+4. 使用B设备申请对此条记录，拆分1手。观察A设备字段
+5. 再次观察总仓字段数值</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t>1. _
-2. 组合保证金为后台查取。拆分后保证金为两腿期权单独保证金相加；组合要低于拆分后</t>
+2. 总仓展示2、可拆展示2
+3. B设备上总仓展示2、可拆展示2
+4. 各字段填入正确，三端比较一致
+5. 总仓展示2、可拆展示1</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2694,7 +2710,7 @@
       <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>期权组合&gt;组合持仓列表排序</t>
+          <t>期权组合&gt;字段：组合保证金、拆分后保证金</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2705,73 +2721,131 @@
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr">
         <is>
+          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx
+2. 账户中拥有50ETFM2504P2400、P2600、P2800 空仓各3手，50ETFM2504P2500、P2700 多仓各3手</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前使用ETF期权  看涨牛市测试背景，事先已组合2手，当前可组1手，可拆2手
+2. 查看此条记录的组合保证金、拆分后保证金字段数值</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 组合保证金为后台查取。拆分后保证金为两腿期权单独保证金相加；组合要低于拆分后</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>期权组合&gt;组合持仓列表排序</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>1. 观察默认进入组合持仓列表，列表排序规则
 2. 尝试点击组合类型列头
 3. 尝试依次点击其余列头</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>1. 按组合类型排序
 2. 不支持用户点击更改正序、倒序
 3. 其余列头均不支持用户点击排序</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr"/>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>期权组合&gt;点组合持仓回填</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx
+2. 账户中拥有50ETFM2504P2400、P2600、P2800 空仓各3手，50ETFM2504P2500、P2700 多仓各3手</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>1. 当前使用ETF期权  看涨牛市测试背景，事先已组合2手，当前可组1手，可拆2手
 2. 重新进入界面，确保上方内容皆为空，无任何数据填入
@@ -2779,7 +2853,7 @@
 4. 校验此时的可组可拆数量</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>1. _
 2. _
@@ -2787,109 +2861,110 @@
 4. 可组可拆数量一致</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr"/>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>期权组合&gt;组合委托列表</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr"/>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx
+2. 账户中拥有50ETFM2504P2400、P2600、P2800 空仓各3手，50ETFM2504P2500、P2700 多仓各3手</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>1. 当前使用ETF期权  看涨牛市测试背景，事先已申请过组合，有失败、成功、挂单中的委托
 2. 查看下方列头内容
 3. 查看下方列表内容</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>1. _
 2. 列头展示：委托时间、组合类型、状态、组合方向（组合/拆分）、合约代码（双行）、方向（双行）、委托量、组合编号、反馈信息。
 3. 各字段填入正确，三端比较一致</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr"/>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>期权组合&gt;组合委托列表排序</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>1. 观察默认进入组合委托列表，列表排序规则
 2. 尝试点击默认时间列头
@@ -2898,7 +2973,7 @@
 5. 退出期权组合界面，重新进入，观察组合委托的排序保存情况</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>1. 按默认时间排序由新到旧排序
 2. 用户可以点击更改正序、倒序
@@ -2907,51 +2982,52 @@
 5. 排序结果不保存，进来又恢复成默认时间由新到旧排序</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr"/>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>期权组合&gt;点组合委托撤单</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr"/>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx
+2. 账户中拥有50ETFM2504P2400、P2600、P2800 空仓各3手，50ETFM2504P2500、P2700 多仓各3手</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>1. 当前使用ETF期权  看涨牛市测试背景，事先已申请过组合，有失败、成功、挂单中的委托
 2. 点击委托列表中失败的委托
@@ -2961,7 +3037,7 @@
 6. 点击【确定】</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>1. _
 2. 点击无反应
@@ -2971,52 +3047,52 @@
 6. 撤单成功，该条委托状态从“申请中”更改为“已撤单”</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr"/>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>其余逻辑&gt;可用都为0，进入界面</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx
 2. 账户中拥有50ETFM2504C2500 多仓5手，50ETFM2504C2600 空仓3手。并都挂排队价占据可用</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>1. 事先将C2500 多仓、C2600 空仓，分别以排队价平仓，使得可用为0手，但总仓依旧在
 2. 当前处于期权组合的界面
@@ -3026,7 +3102,7 @@
 6. 下拉合约2</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>1. _
 2. _
@@ -3036,52 +3112,52 @@
 6. 右腿合约展示C2600  空仓</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr"/>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>其余逻辑&gt;在界面内不再刷新持仓</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr"/>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx
 2. 账户中拥有50ETFM2504C2500 多仓5手，50ETFM2504C2600 空仓3手。并都挂排队价占据可用</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>1. 当前处于期权组合的界面
 2. 在另一台手机终端上，对同一账号进行下单，开仓出来C2700的空仓
@@ -3093,7 +3169,7 @@
 8. 重复步骤到下拉合约2</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>1. _
 2. _
@@ -3105,167 +3181,167 @@
 8. 下拉合约2里，这才刷新持仓，展示C2600、C2700  的空仓</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr"/>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>其余逻辑&gt;合并行权会在持仓列表里占据可用</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr"/>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>1. 当前持仓中有A2507C4000多仓2手，C3800空仓1手
 2. 组合申请中，申请一手买入垂直价差
 3. 返回持仓列表，观察C4000与C3800的持仓</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>1. _
 2. _
 3. C4000可用还剩1手，C3800可用为0</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr"/>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>其余逻辑&gt;投机套保ETF</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr"/>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>1. 当前投保设置为套保
 2. 下单开仓ETF股指期权
 3. 观察委托列表里的投保字段</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>1. _
 2. _
 3. 依旧是投机，ETF股指期权下单只有投机仓</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr"/>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>其余逻辑&gt;投机套保大商所</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr"/>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>1. 下单大商所投机的A2507C4000，多仓1手，套保的A2507C3800，空仓1手
 2. 等待完全成交后，进入期权组合界面
@@ -3274,7 +3350,7 @@
 5. 观察原持仓列表中的C4000  投机仓与C3800  套保仓</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>1. _
 2. _
@@ -3283,72 +3359,14 @@
 5. 可用都被占用</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
         <is>
           <t>P3</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr"/>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>备兑转换&gt;合约代码只展示空仓看涨期权</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr"/>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>1. 账户中拥有50ETFM2504P2400 空仓3手，50ETFM2504C2400 空仓3手，50ETFM2504P2600 空仓3手，50ETFM2504C2700 空仓3手，50ETFM2504P2800 空仓3手
-2. 当前处于备兑转换界面
-3. 点击合约代码观察下拉内容</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>1. _
-2. _
-3. 只展示空仓看涨期权，显示C2400  空仓、C2700  空仓</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3366,7 +3384,7 @@
       <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>备兑转换&gt;备兑类型</t>
+          <t>备兑转换&gt;合约代码只展示空仓看涨期权</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3387,14 +3405,16 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>1. 当前处于备兑转换界面
-2. 点击备兑类型观察下拉内容</t>
+          <t>1. 账户中拥有50ETFM2504C2400、C2700、P2400、P2600、P2800 多仓各1手
+2. 当前处于备兑转换界面
+3. 点击合约代码观察下拉内容</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>1. _
-2. 只展示空仓看涨期权，显示C2400  空仓、C2700  空仓</t>
+2. _
+3. 只展示空仓看涨期权，显示C2400  空仓、C2700  空仓</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -3404,7 +3424,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3422,7 +3442,7 @@
       <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>备兑转换&gt;转换数量</t>
+          <t>备兑转换&gt;备兑类型</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -3444,13 +3464,13 @@
       <c r="G49" s="2" t="inlineStr">
         <is>
           <t>1. 当前处于备兑转换界面
-2. 观察转换数量默认值</t>
+2. 点击备兑类型观察下拉内容</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
           <t>1. _
-2. 转换数量默认为1，后跟可转换的最大手数  可用</t>
+2. 只展示空仓看涨期权，显示C2400  空仓、C2700  空仓</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -3478,7 +3498,7 @@
       <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>备兑转换&gt;转换数量键盘测验</t>
+          <t>备兑转换&gt;转换数量</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3498,6 +3518,62 @@
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于备兑转换界面
+2. 观察转换数量默认值</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 转换数量默认为1，后跟可转换的最大手数  可用</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>备兑转换&gt;转换数量键盘测验</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>1. 点击转换数量
 2. 输入数字5
@@ -3506,7 +3582,7 @@
 5. 点击删除按钮</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>1. 弹出不带小数点、负号的正整数键盘
 2. 5将1替换，而非在1后方续写5变为15
@@ -3515,51 +3591,51 @@
 5. 5数字被正确删除</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr"/>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>备兑转换&gt;锁定弹框</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr"/>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>1. 事先账户拥有5手50ETFM2506C2600  空仓期权持仓
 2. 与其对应证券合约拥有30000股 50ETF股票
@@ -3568,7 +3644,7 @@
 5. 再次输入20000股，锁定</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>1. _
 2. _
@@ -3577,173 +3653,175 @@
 5. 锁定框内展示30000股，同时可用显示3手</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr"/>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>备兑转换&gt;可用计算</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr"/>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr"/>
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>1. 事先账户拥有5手50ETFM2506C2600  空仓期权持仓
 2. 与其对应证券合约拥有30000股 50ETF股票，并且已锁定
 3. 查看可用</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>1. _
 2. _
 3. 可用计算，10000股:1手，可用显示3手</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr"/>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>备兑转换&gt;申请备兑成功流程</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr"/>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>1. 事先账户拥有5手50ETFM2506C2600  空仓期权持仓
 2. 与其对应证券合约拥有30000股 50ETF股票，并且已锁定，此时可用显示3手
 3. 转换数量输入2手，备兑类型选择 普通转备兑
 4. 点击【申请备兑】
 5. 点击【取消】
-6. 重复步骤3，点击【确定】</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
+6. 重复步骤3，点击【确定】
+7. 退出界面，进入交易相关 - 交易日志</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>1. _
 2. _
 3. _
 4. 弹出发单弹框提示，内容2手申请备兑
 5. 弹框关闭无事发生
-6. 成功申请备兑，底下持仓列表原5手非备兑持仓变为2手备兑持仓+3手非备兑持仓，转换委托多一条成功记录；可用更新为1</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
+6. 成功申请备兑，底下持仓列表原5手非备兑持仓变为2手备兑持仓+3手非备兑持仓，转换委托多一条成功记录；可用更新为1
+7. 交易日志中也展示  展示合约代码、备兑类型、转换数量</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr"/>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>备兑转换&gt;申请备兑超出可用数量</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr"/>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr"/>
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>1. 事先账户拥有5手50ETFM2506C2600  空仓期权持仓
 2. 与其对应证券合约拥有30000股 50ETF股票，并且已锁定，此时可用显示3手
@@ -3754,7 +3832,7 @@
 7. 点击【确定】</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>1. _
 2. _
@@ -3765,120 +3843,62 @@
 7. 申请失败，底下组合持仓列表不变化，转换委托列表多一条失败委托记录；</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr"/>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>备兑转换&gt;持仓列表</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr"/>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>1. 事先账户拥有5手50ETFM2506C2600  空仓期权持仓
 2. 查看下方列头内容
 3. 查看下方列表内容</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>1. _
 2. 列头展示：合约名、方向、备兑（备兑/非备兑）、总仓、可用、开仓均价、逐笔浮盈、保证金。
 3. 各字段填入正确，三端比较一致</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr"/>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>备兑转换&gt;持仓列表只展示空仓看涨期权</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr"/>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>1. 事先账户拥有1手50ETFM2506C2600  空仓期权持仓、1手50ETFM2506P2600  空仓期权持仓、1手50ETFM2506C2600  多仓期权持仓
-2. 查看下方列表内容
-3. 与此同时，下拉上方的合约名</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>1. _
-2. 只有一条  C2600  空仓期权持仓的持仓记录
-3. 也只有一条  C2600  空仓期权持仓的持仓记录。这俩选取范围一致</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -3906,7 +3926,7 @@
       <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>备兑转换&gt;持仓列表排序</t>
+          <t>备兑转换&gt;持仓列表只展示空仓看涨期权</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3926,6 +3946,64 @@
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>1. 事先账户拥有50ETFM2506C2600、P2600  空仓各1手，C2600  多仓1手
+2. 查看下方列表内容
+3. 与此同时，下拉上方的合约名</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 只有一条  C2600  空仓期权持仓的持仓记录
+3. 也只有一条  C2600  空仓期权持仓的持仓记录。这俩选取范围一致</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>备兑转换&gt;持仓列表排序</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>1. 观察默认进入持仓列表，列表排序规则
 2. 尝试点击合约名列头
@@ -3934,7 +4012,7 @@
 5. 退出备兑转换界面，重新进入，观察备兑的排序保存情况</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>1. 按合约名排序
 2. 用户可以点击更改正序、倒序
@@ -3943,167 +4021,167 @@
 5. 排序结果不保存，进来又恢复成按合约名排序</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr"/>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>备兑转换&gt;点持仓回填</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr"/>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>备兑转换&gt;点持仓不回填</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr"/>
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. 事先账户拥有5手50ETFM2506C2600  空仓期权持仓
 2. 重新进入界面，确保上方内容皆为空，无任何数据填入
 3. 点击C2600  空仓期权持仓</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>1. _
 2. _
-3. 该持仓相关信息自动回填</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
+3. 不会回填到期权中</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr"/>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>备兑转换&gt;转换委托列表</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr"/>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>1. 事先账户拥有5手50ETFM2506C2600  空仓期权持仓。事先已申请过备兑，有失败、成功
 2. 查看下方列头内容
 3. 查看下方列表内容</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>1. _
 2. 列头展示：合约名、委托类型、状态、委托量、委托时间、反馈信息。
 3. 各字段填入正确，三端比较一致</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr"/>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>备兑转换&gt;转换委托列表排序</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr"/>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr"/>
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>1. 观察默认进入组合委托列表，列表排序规则
 2. 尝试点击默认时间列头
@@ -4112,7 +4190,7 @@
 5. 退出备兑转换界面，重新进入，观察转换委托的排序保存情况</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>1. 按默认时间排序由新到旧排序
 2. 不支持用户点击更改正序、倒序
@@ -4121,72 +4199,14 @@
 5. 排序结果不保存，进来又恢复成默认时间由新到旧排序</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
         <is>
           <t>P3</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr"/>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>合并行权&gt;看涨输入栏中只展示C期权</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr"/>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>1. 账户中拥有50ETFM2504P2400 空仓3手，50ETFM2504C2400 多仓3手，50ETFM2504P2600 空仓3手，50ETFM2504C2700 空仓3手，50ETFM2504P2800 空仓3手
-2. 当前处于合并行权界面
-3. 点击合约代码观察下拉内容</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>1. _
-2. _
-3. 只展示看涨期权，显示C2400  多仓、C2700  空仓</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4204,7 +4224,7 @@
       <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>合并行权&gt;看跌输入栏中只展示P期权</t>
+          <t>合并行权&gt;看涨输入栏中只展示C期权</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4225,7 +4245,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>1. 账户中拥有50ETFM2504P2400 空仓3手，50ETFM2504C2400 多仓3手，50ETFM2504P2600 空仓3手，50ETFM2504C2700 空仓3手，50ETFM2504P2800 多仓3手
+          <t>1. 账户中拥有50ETFM2504C2400、C2700、P2400、P2600、P2800 多仓各1手
 2. 当前处于合并行权界面
 3. 点击合约代码观察下拉内容</t>
         </is>
@@ -4234,7 +4254,7 @@
         <is>
           <t>1. _
 2. _
-3. 只展示看涨期权，显示P2400  空仓、P2600  空仓、P2800  多仓</t>
+3. 只展示看涨期权，显示C2400  多仓、C2700  空仓</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -4262,7 +4282,7 @@
       <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>合并行权&gt;看涨期权执行价低于看跌期权</t>
+          <t>合并行权&gt;看跌输入栏中只展示P期权</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -4283,13 +4303,71 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>1. 账户中拥有50ETFM2504P2400 多仓3手，50ETFM2504C2400 多仓3手，50ETFM2504P2600 多仓3手，50ETFM2504C2700 多仓3手，50ETFM2504P2800 多仓3手
+          <t>1. 账户中拥有50ETFM2504C2400、C2700、P2400、P2600、P2800 多仓各1手
+2. 当前处于合并行权界面
+3. 点击合约代码观察下拉内容</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 只展示看涨期权，显示P2400  空仓、P2600  空仓、P2800  多仓</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>合并行权&gt;看涨期权执行价低于看跌期权</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>1. 账户中拥有50ETFM2504C2400、C2700、P2400、P2600、P2800 多仓各1手
 2. 当前处于合并行权界面
 3. 选择看涨期权为C2700，点击下拉看跌期权
 4. 更改看涨期权为C2400，点击下拉看跌期权</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>1. _
 2. _
@@ -4297,70 +4375,14 @@
 4. 看跌期权可以下拉P2600、P2800可选</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
         <is>
           <t>P2</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr"/>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>合并行权&gt;数量</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr"/>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>1. 当前处于合并行权界面
-2. 观察数量默认值</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>1. _
-2. 转换数量默认为1，后跟可合并行权的最大手数  可用</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>P3</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -4378,7 +4400,7 @@
       <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>合并行权&gt;复位</t>
+          <t>合并行权&gt;数量</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -4398,6 +4420,62 @@
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于合并行权界面
+2. 观察数量默认值</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 转换数量默认为1，后跟可合并行权的最大手数  可用</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>合并行权&gt;复位</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. 当前处于合并行权界面
 2. 修改看涨期权、看跌期权为持仓的期权
@@ -4405,7 +4483,7 @@
 4. 点击【复位】</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>1. _
 2. _
@@ -4413,117 +4491,119 @@
 4. 两个期权合约被清空，数量恢复为1</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr"/>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>合并行权&gt;行权成功流程</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr"/>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr"/>
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>1. 账户中拥有50ETFM2504P2400 多仓3手，50ETFM2504C2400 多仓3手，50ETFM2504P2600 多仓3手，50ETFM2504C2700 多仓3手，50ETFM2504P2800 多仓3手
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>1. 账户中拥有50ETFM2504C2400、C2700、P2400、P2600、P2800 多仓各1手
 2. 看涨期权选择C2400，看跌期权选择P2800
 3. 观察可用
 4. 输入1手，点击【行权】
 5. 点击【取消】
-6. 重复步骤3，点击【确定】</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
+6. 重复步骤3，点击【确定】
+7. 退出界面，进入交易相关 - 交易日志</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>1. _
 2. _
 3. 可用显示3手
-4. 弹出发单弹框提示，内容1手组合行权
+4. 弹出发单弹框提示，内容标题为【确认下单】展示看涨合约、看跌合约、手数
 5. 弹框关闭无事发生
-6. 成功发出行权，底下持仓列表原3手可行全量变为2手，行权委托多一条成功记录；可用更新为2</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
+6. 成功发出行权，底下持仓列表原3手可行全量变为2手，行权委托多一条成功记录；可用更新为2
+7. 交易日志中也展示  展示看涨合约、看跌合约、手数</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr"/>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>合并行权&gt;行权超出可用数量</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr"/>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>1. 账户中拥有50ETFM2504P2400 多仓3手，50ETFM2504C2400 多仓3手，50ETFM2504P2600 多仓3手，50ETFM2504C2700 多仓3手，50ETFM2504P2800 多仓3手
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>1. 账户中拥有50ETFM2504C2400、C2700、P2400、P2600、P2800 多仓各1手
 2. 看涨期权选择C2400，看跌期权选择P2800
 3. 观察可用
 4. 输入5手，点击【行权】
@@ -4532,7 +4612,7 @@
 7. 点击【确定】</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>1. _
 2. _
@@ -4543,118 +4623,62 @@
 7. 申请失败，底下组合持仓列表不变化，行权委托列表多一条失败委托记录；</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr"/>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>合并行权&gt;期权多仓</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr"/>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr"/>
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. 事先账户拥有5手50ETFM2506C2600  多仓期权持仓
 2. 查看下方列头内容
 3. 查看下方列表内容</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>1. _
 2. 列头展示：合约名、总仓、可行权量、行权价值、到期日、开仓均价、逐笔浮盈、保证金、市值、delta；其中，行权价值 = （标的最新价-执行价）* 手数 * 每手乘数。
 3. 各字段填入正确，三端比较一致</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr"/>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>合并行权&gt;期权多仓列表只展示多仓期权</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr"/>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>1. 事先账户拥有1手50ETFM2506C2500  空仓期权持仓、1手50ETFM2506P2600  多仓期权持仓、1手50ETFM2506C2500  多仓期权持仓
-2. 查看下方列表内容</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>1. _
-2. 列表只显示P2600、C2500的多仓，不显示空仓</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -4682,7 +4706,7 @@
       <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>合并行权&gt;期权多仓列表排序</t>
+          <t>合并行权&gt;期权多仓列表只展示多仓期权</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4702,85 +4726,83 @@
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>1. 事先账户拥有50ETFM2506C2500  空仓1手、50ETFM2506C2500、P2600  多仓各1手
+2. 查看下方列表内容</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 列表只显示P2600、C2500的多仓，不显示空仓</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>合并行权&gt;期权多仓列表排序</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr"/>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>1. 观察默认进入期权多仓列表，列表排序规则
 2. 尝试点击合约名列头
 3. 尝试依次点击其余列头</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>1. 按合约名排序
 2. 不支持用户点击更改正序、倒序
 3. 其余列头均不支持用户点击排序</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
         <is>
           <t>P3</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr"/>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>合并行权&gt;点持仓不回填</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr"/>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>1. 事先账户拥有1手50ETFM2506C2500  空仓期权持仓、1手50ETFM2506P2600  多仓期权持仓、1手50ETFM2506C2500  多仓期权持仓
-2. 点击C2500  多仓期权持仓
-3. 点击P2600  多仓期权持仓</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>1. _
-2. 不会回填到看涨期权中
-3. 不会回填到看跌期权中</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -4798,7 +4820,7 @@
       <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>合并行权&gt;行权委托列表</t>
+          <t>合并行权&gt;点持仓不回填</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4819,16 +4841,16 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>1. 事先账户拥有1手50ETFM2506C2500  空仓期权持仓、1手50ETFM2506P2600  多仓期权持仓、1手50ETFM2506C2500  多仓期权持仓。事先已下出C2500、P2600的行权委托
-2. 查看下方列头内容
-3. 查看下方列表内容</t>
+          <t>1. 事先账户拥有50ETFM2506C2500、P2600  多仓各1手
+2. 点击C2500  多仓期权持仓
+3. 点击P2600  多仓期权持仓</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
           <t>1. _
-2. 列头展示：合约名（双行）、状态、委托量、下单时间、行权编号
-3. 各字段填入正确，三端比较一致</t>
+2. 不会回填到看涨期权中
+3. 不会回填到看跌期权中</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -4856,7 +4878,7 @@
       <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>合并行权&gt;转换委托列表排序</t>
+          <t>合并行权&gt;行权委托列表</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4876,6 +4898,64 @@
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>1. 事先账户拥有1手50ETFM2506C2500  空仓；P2600、C2500  多仓各1手。事先已下出C2500、P2600的行权委托
+2. 查看下方列头内容
+3. 查看下方列表内容</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 列头展示：合约名（双行）、状态、委托量、下单时间、行权编号
+3. 各字段填入正确，三端比较一致</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>合并行权&gt;转换委托列表排序</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>/v3.8.0/股票期权支持组合、合并行权/</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr"/>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前已登录了期权交易账号 兴证期货 个股（测试） 32200319  1QAZ2wsx</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>1. 观察默认进入转换委托列表，列表排序规则
 2. 尝试点击默认时间列头
@@ -4884,7 +4964,7 @@
 5. 退出合并行权界面，重新进入，观察默认时间的排序保存情况</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>1. 按默认时间排序由新到旧排序
 2. 用户可以点击更改正序、倒序
@@ -4893,60 +4973,14 @@
 5. 排序结果不保存，进来又恢复成默认时间由新到旧排序</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
         <is>
           <t>P3</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr"/>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>多股同列&gt;多股同列副图指标限制放开</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/期权保证金算法/</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr"/>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr"/>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -4964,12 +4998,12 @@
       <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>多股同列&gt;K线指标功能放开</t>
+          <t>三键下单期权可开手数</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>/v3.8.0/期权保证金算法/</t>
+          <t>/v3.8.0/期权保证金可开算法调整/</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr"/>
@@ -4983,8 +5017,22 @@
           <t>无</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于沪金期权三键下单交易面板
+2. 点击手数，展开手数键盘
+3. 观察界面上的可开手数
+4. 比对三端保证金</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 买期权可开与旧版一致，卖期权相比旧版明显变多，保证金减少
+4. 三端保证金数值一致</t>
+        </is>
+      </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
           <t>STEP</t>
@@ -5010,12 +5058,12 @@
       <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>多股同列&gt;恢复分时图半透明效果</t>
+          <t>闪电下单期权可开手数</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>/v3.8.0/期权保证金算法/</t>
+          <t>/v3.8.0/期权保证金可开算法调整/</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
@@ -5029,8 +5077,22 @@
           <t>无</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于沪金期权闪电下单交易面板
+2. 点击手数，展开手数键盘
+3. 观察界面上的可开手数
+4. 比对三端保证金</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 买期权可开与旧版一致，卖期权相比旧版明显变多，保证金减少
+4. 三端保证金数值一致</t>
+        </is>
+      </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
           <t>STEP</t>
@@ -5056,12 +5118,12 @@
       <c r="A77" s="2" t="inlineStr"/>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>交易&gt;多账号登录支持，多账号登出支持</t>
+          <t>传统下单期权可开手数</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>/v3.8.0/期权保证金算法/</t>
+          <t>/v3.8.0/期权保证金可开算法调整/</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr"/>
@@ -5075,8 +5137,24 @@
           <t>无</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于沪金期权传统下单交易面板
+2. 点击手数，展开手数键盘
+3. 选择买开方向，查看可开手数
+4. 选择卖开方向，查看可开手数
+5. 比对三端保证金</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 买期权可开与旧版一致，保证金减少
+4. 卖期权相比旧版明显变多，保证金减少
+5. 三端保证金数值一致</t>
+        </is>
+      </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
           <t>STEP</t>
@@ -5084,7 +5162,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -5102,12 +5180,12 @@
       <c r="A78" s="2" t="inlineStr"/>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>交易&gt;三键下单可支持套保下单</t>
+          <t>云条件单可开手数</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>/v3.8.0/期权保证金算法/</t>
+          <t>/v3.8.0/期权保证金可开算法调整/</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
@@ -5121,8 +5199,24 @@
           <t>无</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于沪金期权云条件单面板
+2. 点击手数，展开手数键盘
+3. 选择买开方向，查看可开手数
+4. 选择卖开方向，查看可开手数
+5. 比对三端保证金</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 买期权可开与旧版一致，保证金减少
+4. 卖期权相比旧版明显变多，保证金减少
+5. 三端保证金数值一致</t>
+        </is>
+      </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
           <t>STEP</t>
@@ -5130,7 +5224,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -5148,12 +5242,12 @@
       <c r="A79" s="2" t="inlineStr"/>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>传统下单可支持套保下单&gt;bug-41356</t>
+          <t>画线下单可开手数</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>/v3.8.0/期权保证金算法/</t>
+          <t>/v3.8.0/期权保证金可开算法调整/</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
@@ -5167,8 +5261,24 @@
           <t>无</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于沪金期权画线下单面板
+2. 点击手数，展开手数键盘
+3. 选择买开方向，查看可开手数
+4. 选择卖开方向，查看可开手数
+5. 比对三端保证金</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 买期权可开与旧版一致，保证金减少
+4. 卖期权相比旧版明显变多，保证金减少
+5. 三端保证金数值一致</t>
+        </is>
+      </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
           <t>STEP</t>
@@ -5176,7 +5286,7 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -5194,12 +5304,12 @@
       <c r="A80" s="2" t="inlineStr"/>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>传统下单可支持套保下单&gt;投机按钮不再置灰</t>
+          <t>期权策略下单可开手数</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>/v3.8.0/期权保证金算法/</t>
+          <t>/v3.8.0/期权保证金可开算法调整/</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr"/>
@@ -5213,8 +5323,22 @@
           <t>无</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于沪金期权策略下单交易面板
+2. 点击手数，展开手数键盘
+3. 观察界面上的可开手数
+4. 比对三端保证金</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 买期权可开与旧版一致，卖期权相比旧版明显变多，保证金减少
+4. 三端保证金数值一致</t>
+        </is>
+      </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
           <t>STEP</t>
@@ -5222,7 +5346,7 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -5240,12 +5364,12 @@
       <c r="A81" s="2" t="inlineStr"/>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>交易&gt;顶部字体再做放大</t>
+          <t>配置入口</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>/v3.8.0/期权保证金算法/</t>
+          <t>/v3.8.0/持仓增加权利金/</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr"/>
@@ -5259,8 +5383,22 @@
           <t>无</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于交易设置界面
+2. 点击进入【交易列表抬头设置】
+3. 点击进入【持仓列表抬头设置】
+4. 查看市值、虚实值中间部分</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. _
+4. 新增了【权利金】字段可配置，默认处于可添加列头中</t>
+        </is>
+      </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
           <t>STEP</t>
@@ -5268,7 +5406,7 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -5286,18 +5424,18 @@
       <c r="A82" s="2" t="inlineStr"/>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>右菜单&gt;支持多账号登录</t>
+          <t>期权持仓多仓为负，空仓为正</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>/v3.8.0/期权保证金算法/</t>
+          <t>/v3.8.0/持仓增加权利金/</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>1. 当前配置中，已展示“权利金”字段</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -5305,8 +5443,20 @@
           <t>无</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前持仓中有沪金期权的多仓、空仓
+2. 观察多仓权利金字段
+3. 观察空仓权利金字段</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 权利金为负值
+3. 权利金为正值</t>
+        </is>
+      </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
           <t>STEP</t>
@@ -5314,7 +5464,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -5332,18 +5482,18 @@
       <c r="A83" s="2" t="inlineStr"/>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>设置&gt;支持投机套保设置，选项展示出来，默认投机</t>
+          <t>期货持仓权利金字段为--</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>/v3.8.0/期权保证金算法/</t>
+          <t>/v3.8.0/持仓增加权利金/</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>1. 当前配置中，已展示“权利金”字段</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -5351,8 +5501,20 @@
           <t>无</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前持仓中有沪金期货的多仓、空仓
+2. 观察期货多仓权利金字段
+3. 观察期货空仓权利金字段</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 权利金为--
+3. 权利金为--</t>
+        </is>
+      </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
           <t>STEP</t>
@@ -5360,7 +5522,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -5378,18 +5540,18 @@
       <c r="A84" s="2" t="inlineStr"/>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>K线&gt;画线功能放开</t>
+          <t>权利金合计计算</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>/v3.8.0/期权保证金算法/</t>
+          <t>/v3.8.0/持仓增加权利金/</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr"/>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>1. 当前配置中，已展示“权利金”字段</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -5397,8 +5559,20 @@
           <t>无</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前持仓中有沪金期权的多仓、空仓
+2. 观察权利金合计
+3. 比较三端权利金合计</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 权利金合计为正负值数值正确相加
+3. 三端权利金合计一致，刷新正确</t>
+        </is>
+      </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
           <t>STEP</t>
@@ -5406,7 +5580,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -5424,18 +5598,18 @@
       <c r="A85" s="2" t="inlineStr"/>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>K线&gt;竖屏副图支持2个，功能放开</t>
+          <t>成交记录权利金</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>/v3.8.0/期权保证金算法/</t>
+          <t>/v3.8.0/持仓增加权利金/</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr"/>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>1. 当前配置中，已展示“权利金”字段</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -5443,8 +5617,24 @@
           <t>无</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>1. 事先未开过沪金期权的老仓
+2. 测试当日开仓1手沪金期权的多仓，权利金显示X
+3. 比较对比持仓列表与成交列表的，权利金字段
+4. 再开仓2手相同的沪金期权多仓
+5. 比较对比持仓列表与成交列表的，权利金字段</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 两者字段数值一致，都为X
+4. _
+5. 持仓列表里显示权利金为3X，成交列表里则为3条成交记录，分别为X</t>
+        </is>
+      </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
           <t>STEP</t>
@@ -5452,7 +5642,7 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -5461,190 +5651,6 @@
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr"/>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>K线&gt;横屏下也支持画线</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/期权保证金算法/</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr"/>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr"/>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr"/>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>自选&gt;支持多板块，与非适老化自选功能一致</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/期权保证金算法/</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr"/>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr"/>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr"/>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>自选&gt;自选合约列表管理，放开  分组管理功能</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/期权保证金算法/</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr"/>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr"/>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="inlineStr">
-        <is>
-          <t>Prepare</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr"/>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>云端同步&gt;当前用不可更改而生效的关爱模式设置上传，实际不可更改的话，不该上传强制值</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>/v3.8.0/期权保证金算法/</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr"/>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr"/>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>STEP</t>
-        </is>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="inlineStr">
         <is>
           <t>Prepare</t>
         </is>

--- a/tempFiles/testcases.xlsx
+++ b/tempFiles/testcases.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" outlineLevel="1" width="13" customWidth="1" min="1" max="1"/>
@@ -506,18 +506,18 @@
       <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>大单成交记录账号，列表内字段全放开</t>
+          <t>不支持行情叠加&gt;外盘合约</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>/v3.8.37/持仓成交委托动态扩展/</t>
+          <t>/v4.1.0/行情叠加适配期权品种/</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>1. 当前已构造10000条委托、成交数据</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -527,16 +527,14 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1. 登录大单成交记录账号
-2. 设置里，将委托、成交列表的所有字段都打开
-3. 进入交易面板，上下滑动，观察委托、成交列表</t>
+          <t>1. 当前处于小道指的K线图/分时图界面
+2. 点击展开右菜单</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>1. _
-2. _
-3. app稳定不崩溃，列表上下刷新顺畅，无明显卡顿</t>
+2. 没有【行情叠加】入口，不支持该功能需要隐藏</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -546,7 +544,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -564,18 +562,18 @@
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>大单成交记录账号，断网重连</t>
+          <t>不支持行情叠加&gt;黄金合约</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>/v3.8.37/持仓成交委托动态扩展/</t>
+          <t>/v4.1.0/行情叠加适配期权品种/</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>1. 当前已构造10000条委托、成交数据</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -585,14 +583,14 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1. 登录大单成交记录账号
-2. app断网重连</t>
+          <t>1. 当前处于黄金100g的K线图/分时图界面
+2. 点击展开右菜单</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>1. _
-2. 重连顺利，无明显卡顿，重连回来后记录数字与之前一致。可以正常下单、撤单</t>
+2. 没有【行情叠加】入口，不支持该功能需要隐藏</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -602,7 +600,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -620,18 +618,18 @@
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>大单成交记录账号，多账户切换</t>
+          <t>不支持行情叠加&gt;证券合约</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>/v3.8.37/持仓成交委托动态扩展/</t>
+          <t>/v4.1.0/行情叠加适配期权品种/</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1. 当前已构造10000条委托、成交数据</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -641,16 +639,14 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1. 登录大单成交记录账号
-2. app切换到另一个普通账号
-3. app切换会大单账号</t>
+          <t>1. 当前处于浦东机场的K线图/分时图界面
+2. 点击展开右菜单</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1. _
-2. 普通账号不需要分配过多内存，排查是否有内存浪费风险
-3. 切换顺利，无明显卡顿，切换回来后记录数字与之前一致。可以正常下单、撤单</t>
+2. 没有【行情叠加】入口，不支持该功能需要隐藏</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -660,7 +656,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -678,18 +674,18 @@
       <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>大单成交记录账号，第二日账单确认</t>
+          <t>不支持行情叠加&gt;内盘套利合约</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>/v3.8.37/持仓成交委托动态扩展/</t>
+          <t>/v4.1.0/行情叠加适配期权品种/</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1. 当前已构造10000条委托、成交数据</t>
+          <t>无</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -699,14 +695,14 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1. 昨日构造了大单成交记录账号
-2. 第二日打开，查看账单确认界面</t>
+          <t>1. 当前处于菜粕套利的K线图/分时图界面
+2. 点击展开右菜单</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1. _
-2. 界面可正常打开，确认功能无误，可顺利登录账户</t>
+2. 没有【行情叠加】入口，不支持该功能需要隐藏</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -734,12 +730,12 @@
       <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>测速不用等待全部测完</t>
+          <t>支持行情叠加&gt;内盘期货合约</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>/v3.8.37/启动速度验证/</t>
+          <t>/v4.1.0/行情叠加适配期权品种/</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
@@ -755,14 +751,16 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1. 后台故意配置一个测速极慢的行情
-2. 打开App</t>
+          <t>1. 当前处于瓶片503的K线图/分时图界面
+2. 点击展开右菜单
+3. 点击【行情叠加】文本</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1. _
-2. App优化完后，无需等待该极慢的行情测速完成，可以很快结束启动页</t>
+2. 有【行情叠加】文本入口
+3. 右菜单栏关闭，从页面下方成功弹出行情叠加的弹框界面</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -772,7 +770,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -790,12 +788,12 @@
       <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>管理数据无更新不下载</t>
+          <t>支持行情叠加&gt;内盘期权合约</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>/v3.8.37/启动速度验证/</t>
+          <t>/v4.1.0/行情叠加适配期权品种/</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr"/>
@@ -811,16 +809,16 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1. 后台配置管理数据A
-2. 记录首次启动的时间
-3. 第二次启动，记录启动时间</t>
+          <t>1. 当前处于苹果503P7600  K线图/分时图界面
+2. 点击展开右菜单
+3. 点击【行情叠加】文本</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t>1. _
-2. _
-3. 第二次启动时间明显快于首次</t>
+2. 有【行情叠加】文本入口
+3. 右菜单栏关闭，从页面下方成功弹出行情叠加的弹框界面</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -848,12 +846,12 @@
       <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>管理数据更新才触发下载</t>
+          <t>入口&gt;页面进出</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>/v3.8.37/启动速度验证/</t>
+          <t>/v4.1.0/行情叠加适配期权品种/</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
@@ -869,16 +867,22 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1. 后台配置管理数据A
-2. 记录首次启动的时间
-3. 第二次启动，记录启动时间</t>
+          <t>1. 当前处于瓶片503的K线图/分时图界面
+2. 点击展开右菜单
+3. 点击【行情叠加】文本
+4. 点击取消按钮
+5. 重复步骤2、3
+6. 点击弹框区域以外</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1. _
 2. _
-3. 第二次启动时间明显快于首次</t>
+3. 右菜单栏关闭，从页面下方成功弹出行情叠加的弹框界面
+4. 行情叠加界面被关闭
+5. _
+6. 行情叠加界面也被关闭</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -888,7 +892,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -906,12 +910,12 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>其余app加载验证</t>
+          <t>行情叠加框&gt;UI校验</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>/v3.8.37/启动速度验证/</t>
+          <t>/v4.1.0/行情叠加适配期权品种/</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr"/>
@@ -927,16 +931,20 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1. 检查行情板块是否齐全
-2. 检查品种、合约是否齐全
-3. 检查交易地址是否缺失</t>
+          <t>1. 当前处于瓶片607C8500的日K线行情叠加框界面
+2. 观察标题部分
+3. 观察关联品种部分
+4. 观察自定义部分
+5. 观察两个按钮</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1. 行情板块齐全
-2. 品种、合约齐全
-3. 交易地址无缺失</t>
+          <t>1. _
+2. 标题加粗显示“行情叠加”，右侧有个隐藏主图指标的勾选项，默认不勾选
+3. 默认展示瓶片607+瓶片指数+至多4个瓶片关联的品种，两两排布占据3行，每个品种左侧有勾选框。
+4. 默认右侧没有合约，自定义左侧有勾选框
+5. 左侧灰底白字【取消】、右侧红底白字【开始叠加】按钮</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -946,7 +954,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -964,12 +972,12 @@
       <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>二次认证账户，登录校验</t>
+          <t>行情叠加框&gt;默认关联品种</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>/v3.8.37/交易登录优化/</t>
+          <t>/v4.1.0/行情叠加适配期权品种/</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr"/>
@@ -985,14 +993,18 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1. 登录二次认证账户
-2. 观察交易面板</t>
+          <t>1. 当前处于瓶片607C8500的日K线行情叠加框界面
+2. 观察瓶片期权的默认关联品种
+3. 切换合约到原木2701C850，同样通过右菜单进入，行情叠加框界面
+4. 观察原木期权的默认关联品种指数</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1. 成功通过二次认证
-2. 登录成功，先进交易界面后，持仓随后返回</t>
+          <t>1. _
+2. 默认展示瓶片607+瓶片指数+至多4个瓶片关联的品种，两两排布占据3行，每个品种左侧有勾选框。
+3. _
+4. 默认展示原木2701+原木指数+3个关联的品种，两两排布占据3行，每个品种左侧有勾选框。</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1020,12 +1032,12 @@
       <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>账单确认账户，登录校验</t>
+          <t>行情叠加框&gt;横屏下，点击叠加</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>/v3.8.37/交易登录优化/</t>
+          <t>/v4.1.0/行情叠加适配期权品种/</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr"/>
@@ -1041,14 +1053,20 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1. 登录需账单确认账户
-2. 观察交易面板</t>
+          <t>1. 当前处于瓶片607C8500的横屏  日K线界面
+2. 点击右菜单 - 【行情叠加】
+3. 点击返回，关闭叠加框
+4. 重复步骤3
+5. 勾选PTA指数后，正常【开始叠加】</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1. 账单确认成功
-2. 登录成功，先进交易界面后，持仓随后返回</t>
+          <t>1. _
+2. app会强制回到竖屏，出现竖屏时的叠加框进行操作
+3. app返回横屏
+4. app会强制回到竖屏，出现竖屏时的叠加框进行操作
+5. 开始叠加后，app返回横屏，PTA日K线正确叠加在瓶片503的后方</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1076,12 +1094,12 @@
       <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>重置密码后，登录</t>
+          <t>标的物行情&gt;开启无法关闭</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>/v3.8.37/交易登录优化/</t>
+          <t>/v4.1.0/行情叠加适配期权品种/</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr"/>
@@ -1097,14 +1115,18 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1. 登录需重置密码账户
-2. 观察交易面板</t>
+          <t>1. app从旧版升级到新版
+2. 点击进入沪金2607P1040期权合约的分时图界面
+3. 观察期货版的合约名称下方
+4. 尝试关闭该展示</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1. 密码重置成功，登录
-2. 登录成功，先进交易界面后，持仓随后返回</t>
+          <t>1. _
+2. 默认是期货版风格
+3. 合约名称下方有标的物 沪金2607的行情信息；展示 “标的  沪金2607  最新价  涨跌  涨幅%”标的物黑色，其余3个受涨红跌绿展示颜色
+4. 无法关闭</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1114,7 +1136,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1132,12 +1154,12 @@
       <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>登录后，断网重连</t>
+          <t>标的物行情&gt;展示位置</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>/v3.8.37/交易登录优化/</t>
+          <t>/v4.1.0/行情叠加适配期权品种/</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr"/>
@@ -1153,14 +1175,14 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1. 已登录账号，app断网重连
-2. 观察交易面板</t>
+          <t>1. 当前处于沪金2607P1040期权合约的分时图界面
+2. 观察标的物行情栏位置</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
           <t>1. _
-2. 登录成功，先进交易界面后，持仓随后返回</t>
+2. 默认显示在合约名称下方，若是打开了大单提醒，在大单提醒的上方</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1170,15 +1192,8053 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>标的物行情&gt;刷新时机</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/行情叠加适配期权品种/</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于沪金2607P1040期权合约的分时图界面
+2. 在界面等待，观察标的物行情栏刷新</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 行情栏内行情刷新正确，三段一致</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>july</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>标的物行情&gt;点击跳转</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/行情叠加适配期权品种/</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于沪金2607P1040期权合约的分时图界面
+2. 点击界面上标的物行情栏 右侧的&gt;
+3. 点击系统返回键，或者调用全局返回手势</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 界面从沪金期权合约的行情，跳转到，标的物沪金2607合约行情界面
+3. 正确返回到之前的 沪金期权合约行情？</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>功能入口&gt;入口位置</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前已登录了期货组合交易账号 海通期货  CTP开发 40031427 htqh61871688
+2. 展开右菜单
+3. 点击【期货组合】
+4. 点击左上角的退出按钮，或者调用系统返回</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 成功进入期货组合界面
+4. 可以正确进出界面</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>UI校验&gt;多账号切换栏</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前已登录了期货组合交易账号 海通期货  CTP开发 40031427 htqh61871688</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于期货组合界面
+2. 尝试寻找多账户切换控件</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 无多账号切换控件，不支持切换账号</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>业务校验&gt;组合类型、投保未填入、合约1、合约2不允许修改</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于期货组合的界面
+2. 组合类型、投保尚未全部填入
+3. 尝试点击下拉组合类型、合约1、合约2</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 点击无反应，不允许修改</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>业务校验&gt;组合类型填写范围</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1. 测试账户中没有任何可组组合的期货持仓
+2. 当前处于期货组合的界面
+3. 点击下拉“组合类型”</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 下拉选项无限制，有“组合申请”、“组合对锁”、“组合拆分”3个选项可供选择</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>业务校验&gt;投保填写范围</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1. 测试账户中没有任何可组组合的期货持仓
+2. 当前处于期货组合的界面
+3. 在组合类型未选择的前提下，尝试点击下拉“投保”
+4. 在组合类型选择了“组合申请”后，尝试点击下拉“投保”</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 下拉选项无限制，有“投机-投机”、“投机-套保”、“套保-投机”、“套保-套保”4个选项可供选择
+4. 依旧下拉选项无限制</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>业务校验&gt;组合类型或投保更改，合约1合约2清空</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>1. 账户中拥有p2607（棕榈油）、c2611（玉米）多仓各5手；p2611、c2607  空仓各3手；i2605（铁矿石） 多空分别为4手、8手</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于期货组合的界面
+2. 点击下拉“组合类型”
+3. 点击下拉“投保”
+4. 尝试下拉合约1
+5. 尝试下拉合约2
+6. 更改“投保”为套保-套保
+7. 重复步骤2~5，更改“组合类型”为组合对锁</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 下拉选项无限制，选择组合申请
+3. 下拉选项无限制，选择投机-投机
+4. 合约1选择p2607 多仓
+5. 合约2选择p2611 空仓
+6. 合约1、合约2都清空
+7. 合约1、合约2都清空</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>大商所期货&gt;组合申请：买方向期货跨期组合</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1. 账户中拥有p2607（棕榈油）5手；p2611、c2611  空仓各3手；i2605（铁矿石） 多空分别为4手、8手</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于期货组合的界面
+2. 点击下拉“组合类型”
+3. 点击下拉“投保”
+4. 尝试下拉合约1
+5. 尝试下拉合约2
+6. 委托数量填入
+7. 点击申请
+8. 点击确定</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 下拉选项无限制，选择组合申请
+3. 下拉选项无限制，选择投机-投机
+4. 合约1选择p2607 多仓
+5. 合约2选择p2611 空仓
+6. 默认手数为1，不做修改了
+7. 弹框确认弹框，提示文本中写入 组合类型、投保、合约1、合约2、委托数量
+8. 顶部弹框提醒：已提交，过几秒后，下方委托列表成功展示组合持仓</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>大商所期货&gt;组合申请：卖方向期货跨期组合</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1. 账户中拥有p2607（棕榈油）5手；p2611、c2611  空仓各3手；i2605（铁矿石） 多空分别为4手、8手</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于期货组合的界面
+2. 点击下拉“组合类型”
+3. 点击下拉“投保”
+4. 尝试下拉合约1
+5. 尝试下拉合约2
+6. 委托数量填入
+7. 点击申请
+8. 点击确定</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 下拉选项无限制，选择组合申请
+3. 下拉选项无限制，选择投机-投机
+4. 合约1选择p2611 空仓
+5. 合约2选择p2607 多仓
+6. 默认手数为1，不做修改了
+7. 弹框确认弹框，提示文本中写入 组合类型、投保、合约1、合约2、委托数量
+8. 顶部弹框提醒：已提交，过几秒后，下方委托列表成功展示组合持仓</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>大商所期货&gt;组合申请：买方向期货跨合约组合</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1. 账户中拥有p2607（棕榈油）5手；p2611、c2611  空仓各3手；i2605（铁矿石） 多空分别为4手、8手</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于期货组合的界面
+2. 点击下拉“组合类型”
+3. 点击下拉“投保”
+4. 尝试下拉合约1
+5. 尝试下拉合约2
+6. 委托数量填入
+7. 点击申请
+8. 点击确定</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 下拉选项无限制，选择组合申请
+3. 下拉选项无限制，选择投机-投机
+4. 合约1选择p2607 多仓
+5. 合约2选择c2611 空仓
+6. 默认手数为1，不做修改了
+7. 弹框确认弹框，提示文本中写入 组合类型、投保、合约1、合约2、委托数量
+8. 顶部弹框提醒：已提交，过几秒后，下方委托列表成功展示组合持仓</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>大商所期货&gt;组合申请：卖方向期货跨合约组合</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr"/>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1. 账户中拥有p2607（棕榈油）5手；p2611、c2611  空仓各3手；i2605（铁矿石） 多空分别为4手、8手</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于期货组合的界面
+2. 点击下拉“组合类型”
+3. 点击下拉“投保”
+4. 尝试下拉合约1
+5. 尝试下拉合约2
+6. 委托数量填入
+7. 点击申请
+8. 点击确定</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 下拉选项无限制，选择组合申请
+3. 下拉选项无限制，选择投机-投机
+4. 合约1选择c2611 空仓
+5. 合约2选择p2607 多仓
+6. 默认手数为1，不做修改了
+7. 弹框确认弹框，提示文本中写入 组合类型、投保、合约1、合约2、委托数量
+8. 顶部弹框提醒：已提交，过几秒后，下方委托列表成功展示组合持仓</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>大商所期货&gt;组合对锁：买方向</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1. 账户中拥有p2607（棕榈油）5手；p2611、c2611  空仓各3手；i2605（铁矿石） 多空分别为4手、8手</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于期货组合的界面
+2. 点击下拉“组合类型”
+3. 点击下拉“投保”
+4. 尝试下拉合约1
+5. 尝试下拉合约2
+6. 委托数量填入
+7. 点击申请
+8. 点击确定</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 下拉选项无限制，选择组合对锁
+3. 下拉选项无限制，选择投机-投机
+4. 合约1选择i2605 多仓
+5. 合约2选择i2605 空仓
+6. 默认手数为1，不做修改了
+7. 弹框确认弹框，提示文本中写入 组合类型、投保、合约1、合约2、委托数量
+8. 顶部弹框提醒：已提交，过几秒后，下方委托列表成功展示组合持仓</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>大商所期货&gt;组合对锁：卖方向</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>1. 账户中拥有p2607（棕榈油）5手；p2611、c2611  空仓各3手；i2605（铁矿石） 多空分别为4手、8手</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于期货组合的界面
+2. 点击下拉“组合类型”
+3. 点击下拉“投保”
+4. 尝试下拉合约1</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 下拉选项无限制，选择组合对锁
+3. 下拉选项无限制，选择投机-投机
+4. 合约1选择不到i2605 空仓，业务限制，组合对锁只有买方向</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>大商所期货&gt;组合拆分</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1. 账户中拥有p2607（棕榈油）5手；p2611、c2611  空仓各3手；i2605（铁矿石） 多空分别为4手、8手</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于期货组合的界面
+2. 当前已组成了i2605&amp;i2605  期货对锁组合
+3. 点击下拉“组合类型”
+4. 点击下拉“投保”
+5. 尝试下拉合约1
+6. 尝试下拉合约2
+7. 委托数量填入
+8. 点击申请
+9. 点击确定</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 下拉选项无限制，选择组合拆分
+4. 下拉选项无限制，选择投机-投机
+5. 合约1选择i2605 多仓
+6. 合约2选择i2605 空仓
+7. 默认手数为1，不做修改了
+8. 弹框确认弹框，提示文本中写入 组合类型、投保、合约1、合约2、委托数量
+9. 顶部弹框提醒：已提交，过几秒后，下方委托列表成功展示组合持仓</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>广商所期货&gt;组合申请：买方向期货跨期组合</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1. 账户中拥有ps2607（多晶硅）5手；ps2611、si2611  空仓各3手；lc2605（碳酸锂） 多空分别为4手、8手</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于期货组合的界面
+2. 点击下拉“组合类型”
+3. 点击下拉“投保”
+4. 尝试下拉合约1
+5. 尝试下拉合约2
+6. 委托数量填入
+7. 点击申请
+8. 点击确定</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 下拉选项无限制，选择组合申请
+3. 下拉选项无限制，选择投机-投机
+4. 合约1选择ps2607 多仓
+5. 合约2选择ps2611 空仓
+6. 默认手数为1，不做修改了
+7. 弹框确认弹框，提示文本中写入 组合类型、投保、合约1、合约2、委托数量
+8. 顶部弹框提醒：已提交，过几秒后，下方委托列表成功展示组合持仓</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>广商所期货&gt;组合申请：卖方向期货跨期组合</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>1. 账户中拥有ps2607（多晶硅）5手；ps2611、si2611  空仓各3手；lc2605（碳酸锂） 多空分别为4手、8手</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于期货组合的界面
+2. 点击下拉“组合类型”
+3. 点击下拉“投保”
+4. 尝试下拉合约1
+5. 尝试下拉合约2
+6. 委托数量填入
+7. 点击申请
+8. 点击确定</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 下拉选项无限制，选择组合申请
+3. 下拉选项无限制，选择投机-投机
+4. 合约1选择ps2611 空仓
+5. 合约2选择ps2607 多仓
+6. 默认手数为1，不做修改了
+7. 弹框确认弹框，提示文本中写入 组合类型、投保、合约1、合约2、委托数量
+8. 顶部弹框提醒：已提交，过几秒后，下方委托列表成功展示组合持仓</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>广商所期货&gt;组合申请：买方向期货跨合约组合</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>1. 账户中拥有ps2607（多晶硅）5手；ps2611、si2611  空仓各3手；lc2605（碳酸锂） 多空分别为4手、8手</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于期货组合的界面
+2. 点击下拉“组合类型”
+3. 点击下拉“投保”
+4. 尝试下拉合约1
+5. 尝试下拉合约2
+6. 委托数量填入
+7. 点击申请
+8. 点击确定</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 下拉选项无限制，选择组合申请
+3. 下拉选项无限制，选择投机-投机
+4. 合约1选择ps2607 多仓
+5. 合约2选择si2611 空仓
+6. 默认手数为1，不做修改了
+7. 弹框确认弹框，提示文本中写入 组合类型、投保、合约1、合约2、委托数量
+8. 顶部弹框提醒：已提交，过几秒后，下方委托列表成功展示组合持仓</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>广商所期货&gt;组合申请：卖方向期货跨合约组合</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>1. 账户中拥有ps2607（多晶硅）5手；ps2611、si2611  空仓各3手；lc2605（碳酸锂） 多空分别为4手、8手</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于期货组合的界面
+2. 点击下拉“组合类型”
+3. 点击下拉“投保”
+4. 尝试下拉合约1
+5. 尝试下拉合约2
+6. 委托数量填入
+7. 点击申请
+8. 点击确定</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 下拉选项无限制，选择组合申请
+3. 下拉选项无限制，选择投机-投机
+4. 合约1选择si2611 空仓
+5. 合约2选择ps2607 多仓
+6. 默认手数为1，不做修改了
+7. 弹框确认弹框，提示文本中写入 组合类型、投保、合约1、合约2、委托数量
+8. 顶部弹框提醒：已提交，过几秒后，下方委托列表成功展示组合持仓</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>广商所期货&gt;组合对锁：买方向</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>1. 账户中拥有ps2607（多晶硅）5手；ps2611、si2611  空仓各3手；lc2605（碳酸锂） 多空分别为4手、8手</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于期货组合的界面
+2. 点击下拉“组合类型”
+3. 点击下拉“投保”
+4. 尝试下拉合约1
+5. 尝试下拉合约2
+6. 委托数量填入
+7. 点击申请
+8. 点击确定</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 下拉选项无限制，选择组合对锁
+3. 下拉选项无限制，选择投机-投机
+4. 合约1选择lc2605 多仓
+5. 合约2选择lc2605 空仓
+6. 默认手数为1，不做修改了
+7. 弹框确认弹框，提示文本中写入 组合类型、投保、合约1、合约2、委托数量
+8. 顶部弹框提醒：已提交，过几秒后，下方委托列表成功展示组合持仓</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>广商所期货&gt;组合对锁：卖方向</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>1. 账户中拥有ps2607（多晶硅）5手；ps2611、si2611  空仓各3手；lc2605（碳酸锂） 多空分别为4手、8手</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于期货组合的界面
+2. 点击下拉“组合类型”
+3. 点击下拉“投保”
+4. 尝试下拉合约1</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 下拉选项无限制，选择组合对锁
+3. 下拉选项无限制，选择投机-投机
+4. 合约1选择不到lc2605 空仓，业务限制，组合对锁只有买方向</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>广商所期货&gt;组合拆分</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>1. 账户中拥有ps2607（多晶硅）5手；ps2611、si2611  空仓各3手；lc2605（碳酸锂） 多空分别为4手、8手</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于期货组合的界面
+2. 当前已组成了lc2605&amp;lc2605  期货对锁组合
+3. 点击下拉“组合类型”
+4. 点击下拉“投保”
+5. 尝试下拉合约1
+6. 尝试下拉合约2
+7. 委托数量填入
+8. 点击申请
+9. 点击确定</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 下拉选项无限制，选择组合拆分
+4. 下拉选项无限制，选择投机-投机
+5. 合约1选择lc2605 多仓
+6. 合约2选择lc2605 空仓
+7. 默认手数为1，不做修改了
+8. 弹框确认弹框，提示文本中写入 组合类型、投保、合约1、合约2、委托数量
+9. 顶部弹框提醒：已提交，过几秒后，下方委托列表成功展示组合持仓</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>业务校验&gt;郑商所期货</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>业务校验&gt;可用数量</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>1. 账户中拥有p2607（棕榈油）5手；p2611、c2611  空仓各3手；i2605（铁矿石） 多空分别为4手、8手</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前使用大商所期货对锁的，测试背景
+2. 合约1为i2605 多，合约2为i2605 空
+3. 观察4个选项选完后，计算可组数量
+4. 委托数量填入
+5. 点击申请、确定后，观察可用数量</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 可组数量取左腿、右腿可用的最小值。左腿4手，右腿8手，记为4手
+4. 默认手数为1，不做修改了
+5. 可用数量减为3手</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>业务校验&gt;委托数量默认为1</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前使用大商所期货对锁的，测试背景
+2. 观察4个选项选完后，委托数量展示</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 委托数量默认为1手</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>业务校验&gt;委托数量键盘测验</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>1. 点击委托数量
+2. 输入数字5
+3. 点击+按钮，3下
+4. 长按-按钮，1秒
+5. 点击删除按钮</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>1. 弹出不带小数点、负号的正整数键盘
+2. 5将1替换，而非在1后方续写5变为15
+3. 点击+，5变为6、7、8
+4. 长按触发8快速降低，降低到5
+5. 5数字被正确删除</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>业务校验&gt;申请组合超出可组数量</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>1. 账户中拥有p2607（棕榈油）5手；p2611、c2611  空仓各3手；i2605（铁矿石） 多空分别为4手、8手</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前使用大商所期货对锁的，测试背景
+2. 委托数量输入5手
+3. 点击【申请组合】
+4. 点击【取消】
+5. 重复步骤3，点击【确定】
+6. 点击【确定】</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>1. 该测试场景可用为4手
+2. _
+3. 弹框提示：组合申请手数大于可用持仓量
+4. 弹框关闭无事发生
+5. 弹出发单弹框提示，内容5手组合申请
+6. 组合失败，底下组合持仓列表不变化，组合委托列表多一条失败委托记录；</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>业务校验&gt;申请拆分超出可拆数量</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>1. 账户中拥有p2607（棕榈油）5手；p2611、c2611  空仓各3手；i2605（铁矿石） 多空分别为4手、8手</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前使用大商所期货对锁的，测试背景  事先已组合2手，当前可用2手
+2. 委托数量输入3手
+3. 点击【申请拆分】
+4. 点击【取消】
+5. 重复步骤3，点击【确定】
+6. 点击【确定】</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 弹框提示：组合拆单手数大于组合持仓量
+4. 弹框关闭无事发生
+5. 弹出发单弹框提示，内容2手组合拆分
+6. 拆分失败，底下组合持仓列表不变化，组合委托列表多一条失败委托记录；</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>业务校验&gt;组合持仓列表</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>1. 查看下方列头内容
+2. 查看下方列表内容</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>1. 列头展示：组合合约、总仓、方向、可拆、投保、组合保证金、组合编号
+2. 各字段填入正确，三端比较一致</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>业务校验&gt;跨设备字段刷新</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>1. 账户中拥有p2607（棕榈油）5手；p2611、c2611  空仓各3手；i2605（铁矿石） 多空分别为4手、8手</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前使用大商所期货对锁的，测试背景  事先已组合2手，当前可用2手
+2. 查看此条记录的总仓、可拆字段数值
+3. A设置呆在此界面，再次新开一个B设备进入此界面
+4. 使用B设备申请对此条记录，拆分1手。观察A设备字段
+5. 再次观察总仓字段数值</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 总仓展示2、可拆展示2
+3. B设备上总仓展示2、可拆展示2
+4. 各字段填入正确，三端比较一致
+5. 总仓展示2、可拆展示1</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>业务校验&gt;组合持仓列表排序</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>1. 观察默认进入组合持仓列表，列表排序规则
+2. 尝试点击组合类型列头
+3. 尝试依次点击其余列头</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>1. 按组合类型排序
+2. 不支持用户点击更改正序、倒序
+3. 其余列头均不支持用户点击排序</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>业务校验&gt;点组合持仓回填</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>1. 账户中拥有p2607（棕榈油）5手；p2611、c2611  空仓各3手；i2605（铁矿石） 多空分别为4手、8手</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前使用大商所期货对锁的，测试背景  事先已组合2手，当前可用2手
+2. 重新进入界面，确保上方内容皆为空，无任何数据填入
+3. 点击组合成功的期货对锁
+4. 校验此时的可用数量</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 该持仓相关信息自动回填
+4. 可用数量正确</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>业务校验&gt;组合委托列表</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>1. 账户中拥有p2607（棕榈油）5手；p2611、c2611  空仓各3手；i2605（铁矿石） 多空分别为4手、8手</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前使用大商所期货对锁的，测试背景  事先已组合2手，当前可用2手
+2. 查看下方列头内容
+3. 查看下方列表内容</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 列头展示：委托时间、组合类型、状态、组合方向（组合/拆分）、合约代码、方向、委托量、组合编号、反馈信息。
+3. 各字段填入正确，三端比较一致</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>业务校验&gt;组合委托列表排序</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>1. 观察默认进入组合委托列表，列表排序规则
+2. 尝试点击默认时间列头
+3. 尝试依次点击其余列头
+4. 选择了组合类型排序
+5. 退出期权组合界面，重新进入，观察组合委托的排序保存情况</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>1. 按默认时间排序由新到旧排序
+2. 用户可以点击更改正序、倒序
+3. 除默认时间以外，还有委托时间、组合类型、组合方向可以排序
+4. _
+5. 排序结果不保存，进来又恢复成默认时间由新到旧排序</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>交易日志</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/期货组合申请拆分/</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>不支持大单功能&gt;外盘合约</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于小道指的K线图/分时图界面
+2. 查看大单提醒</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 没有大单功能，需要隐藏</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>不支持大单功能&gt;黄金合约</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于黄金100g的K线图/分时图界面
+2. 查看大单提醒</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 没有大单功能，需要隐藏</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>不支持大单功能&gt;证券合约</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于浦东机场的K线图/分时图界面
+2. 查看大单提醒</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 没有大单功能，需要隐藏</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>不支持大单功能&gt;内盘套利合约</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于菜粕套利的K线图/分时图界面
+2. 查看大单提醒</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 没有大单功能，需要隐藏</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>不支持大单功能&gt;内盘期权合约</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr"/>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于苹果607P7600  K线图/分时图界面
+2. 查看大单提醒</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 没有大单功能，需要隐藏</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>支持大单功能&gt;内盘期货合约</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于瓶片607的K线图/分时图界面
+2. 查看大单提醒</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 展示了大单提醒，支持所有大单功能</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>大单提醒推送&gt;默认开启</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr"/>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>1. app从旧版升级到新版
+2. 点击进入丙烯主力合约的分时图界面
+3. 观察期货版的合约名称下方
+4. 点击右菜单，切换行情展示为证券版风格，返回分时图
+5. 观察证券版的合约名称下方</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 默认是期货版风格
+3. app更新到新版，会默认开启大单推送功能。合约名称下方有丙烯合约的大单提醒信息展示
+4. _
+5. 合约名称下方，周期栏上方有丙烯合约的大单提醒信息展示</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>大单提醒推送&gt;期货版点击箭头跳转</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前行情显示风格为 期货版</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于丙烯主力分时图界面
+2. 点击大单提醒栏的右侧 “&gt;” 图标
+3. 观察成交明细</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 界面从分时跳到了盘口，并且界面上选择了成交明细
+3. 成交明细有做改造，有“全部明细”“大单筛选”“成交统计”三个tab页，跳转后默认选中“大单筛选”页</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>大单提醒推送&gt;证券版点击箭头跳转</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前行情显示风格为 证券版</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于丙烯主力分时图界面
+2. 点击大单提醒栏的右侧 “&gt;” 图标
+3. 观察成交明细</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 界面从图表区域划至下方web区域，并且选择了明细
+3. 成交明细有做改造，有“全部明细”“大单筛选”“成交统计”三个tab页，跳转后默认选中“大单筛选”页</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>大单提醒推送&gt;大单提醒设置页</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前行情显示风格为 证券版</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于丙烯主力分时图界面
+2. 点击大单提醒栏的右侧 “&gt;” 图标
+3. 点击大单筛选右侧的齿轮图表
+4. 观察大单筛选设置
+5. 点击 关闭/开启
+6. 返回分时图界面</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 成功跳转到成交明细 - 大单筛选
+3. 成功跳转大单筛选设置
+4. 首行展示大单提醒，右侧为 关闭/开启 滑块；下方为筛选参数设置项，与大单提醒无关
+5. 成功切换为关闭状态
+6. 大单提醒成功被关闭</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>大单提醒推送&gt;开启/关闭状态长期保存</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr"/>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>1. 接上一条用例，成功关闭大单提醒设置
+2. app重启，重新进入分时图
+3. 观察大单提醒</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 大单提醒功能依旧被关闭，关闭状态长期保存</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>大单提醒推送&gt;大单推送内容显示</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于任意较为活跃的合约分时图界面（瓶片、豆粕）
+2. 查看大单推送内容
+3. 在界面等待，来一笔新大单的推送</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 只显示最新一笔大单：时间、价格、方向、手数
+3. 大单推送栏 由下方往上滑动刷新出新大单的信息内容</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>大单提醒推送&gt;合约过长价格显示</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr"/>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于价格较长的合约分时图界面（沪镍、碳酸锂）
+2. 查看大单推送内容
+3. 在界面等待，来一笔新大单的推送</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 由于价格过长，省略价格，只显示：时间、方向、手数
+3. 大单推送栏 由下方往上滑动刷新出新大单的信息内容</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>大单提醒推送&gt;无大单显示</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于不活跃的合约分时图界面（早稻、粳米）
+2. 查看大单推送内容</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 无大单，显示“至今暂无大单，点击查看更多”</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>全部明细改造&gt;期货版只显示一屏</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr"/>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前行情显示风格为 期货版</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于丙烯主力的成交明细界面
+2. 点击“全部明细”tab
+3. 观察成交明细</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 全部明细分上下两部分，下方列表内容与旧版一致。上方有3个tab切换，当前选中“全部明细”，右侧有大单筛选的配置外显</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>全部明细改造&gt;证券版可下滑查看更多</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前行情显示风格为 证券版</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于丙烯主力的成交明细界面
+2. 点击“全部明细”tab
+3. 观察成交明细</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 全部明细默认展示一屏，可以下滑查看更多。每次新增一屏幕量的明细数据</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>新增大单筛选&gt;页面校验</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于丙烯主力的成交明细界面
+2. 点击“大单筛选”tab
+3. 观察大单筛选界面</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 顶部有配置项外显，默认为：成交倍数&gt;=5倍；下方为筛选后的大单明细列表。列表展示时间、价格、方向、手数；列表最多显示一屏，最新的大单展示在最上方</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>新增大单筛选&gt;在界面等待新大单刷新</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于丙烯主力的大单筛选界面
+2. 在界面等待，有新大单出现
+3. 退出界面，重新进入</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 新大单出现在列表最上方，最下方的大单若展示不下，会被推下。单屏幕内容不可下滑刷新拖动
+3. 大单内容与之前退出时一致</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>新增大单筛选&gt;只统计最近200根</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr"/>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>1. 接上一条用例，记录测试时的大单内容
+2. 等待10分钟，确保已过200个tick
+3. 重新进入大单筛选界面，观察大单列表内容</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>1. 大单内容为A-G
+2. _
+3. 由于只统计最近200tick，大单内容不该有A-G的旧大单信息，而是H-M</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>新增大单筛选&gt;新上市品种不支持大单筛选</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>1. 测试期间，有品种的新合约上市，或者有新合约上市</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于新上市的合约行情界面
+2. 进入其大单筛选页面中</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 由于大单筛选需要上一日的成交量统计平均成交量，发现成交明细里没有 大单筛选tab，功能被隐藏</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>大单筛选配置页&gt;页面校验</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr"/>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于大单筛选tab栏下
+2. 点击右侧的齿轮图标
+3. 观察配置页</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 成功进入大单筛选配置页
+3. 主体内容分两部分，先展示大单提醒的开关控制，此配置与大单提醒推送有关；下方展示筛选参数。分全局筛选、自定义筛选，默认勾选全局筛选。</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>大单筛选配置页&gt;筛选配置选择长期保存</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于大单筛选配置页
+2. 修改筛选项为“自定义筛选”
+3. app重启再次打开
+4. 返回大单筛选配置页，观察选择项</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 自定义筛选前的红框打上勾
+3. _
+4. 筛选配置选择依旧是“自定义筛选”，长期保存</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>大单筛选配置页&gt;全局筛选页面进出</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr"/>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于大单筛选配置页面
+2. 点击全局筛选右侧的 &gt; 箭头图标
+3. 点击取消或界面外遮罩层区域</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 界面由下方往上弹出 全局筛选的配置弹框
+3. 设置弹框被收起，且不保存修改</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>大单筛选配置页&gt;全局筛选默认配置</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于大单筛选配置页面
+2. 点击全局筛选右侧的 &gt; 箭头图标
+3. 观察全局筛选里的默认配置</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 默认为5倍、筛选全部开平方向</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>大单筛选配置页&gt;全局筛选验证配置</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr"/>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于大单筛选配置页面
+2. 点击全局筛选右侧的 &gt; 箭头图标
+3. 将开平方向，由之前的全部打开，调整到只剩多开
+4. 返回大单筛选界面，观察
+5. 再次进入配置
+6. 恢复开平方向，修改成交倍数由5变为20
+7. 返回大单筛选界面，观察</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. _
+4. 大单筛选列表内容明显减少，且只剩  “多开” 方向的大单依旧展示
+5. _
+6. _
+7. 大单筛选列表内容明显减少，不过区别刚刚只有“多开”方向，现在8种方向大单都能展示</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>大单筛选配置页&gt;全局筛选恢复默认</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr"/>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>1. 接上一条用例，记录测试时的配置内容
+2. 点击全局筛选右侧的 &gt; 箭头图标
+3. 点击弹框右上角的 “恢复默认” 按钮
+4. 点击确定</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 弹出确认框“确定恢复默认吗？”
+4. 配置里各项内容恢复成功默认内容</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>大单筛选配置页&gt;全局筛选不合法输入</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr"/>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于大单筛选配置页面
+2. 点击全局筛选右侧的 &gt; 箭头图标
+3. 修改倍数由5变为1000
+4. 再次修改倍数，尝试再加1个1</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 1000为4位数字，支持输入，框内文字成功变为1000
+4. 10001为5位数字，不支持输入，框内文字不变，依旧是1000；并且弹出toast提示：“成交倍数最多输入4位”</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>大单筛选配置页&gt;自定义筛选页面进出</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于PTA2607合约的大单筛选配置页面
+2. 点击自定义筛选右侧的 &gt; 箭头图标
+3. 点击取消或界面外遮罩层区域</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 界面由下方往上弹出 自定义筛选的配置弹框
+3. 设置弹框被收起，且不保存修改</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>大单筛选配置页&gt;自定义筛选默认配置</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr"/>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于PTA2607合约的大单筛选配置页面
+2. 点击自定义筛选右侧的 &gt; 箭头图标
+3. 观察自定义筛选里的默认配置</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 默认成交手数10手、全部开平方向，增减仓手数和价位为空</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>大单筛选配置页&gt;自定义筛选验证配置</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于PTA2607合约的大单筛选配置页面
+2. 点击自定义筛选右侧的 &gt; 箭头图标
+3. 将开平方向，由之前的全部打开，调整到只剩多开
+4. 返回大单筛选界面，观察
+5. 再次进入配置
+6. 恢复开平方向，修改成交手数由10变为100手
+7. 返回大单筛选界面，观察
+8. 再次进入配置
+9. 恢复成交手数，修改增减仓手数，变为100手
+10. 返回大单筛选界面，观察
+11. 再次进入配置
+12. 恢复增减仓手数，修改价位，变为6200~6300
+13. 返回大单筛选界面，观察</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. _
+4. 大单筛选列表内容明显减少，且只剩  “多开” 方向的大单依旧展示
+5. _
+6. _
+7. 大单筛选列表内容明显减少，筛选下来的大单只有100手以上的
+8. _
+9. _
+10. 大单筛选列表内容明显减少，筛选下来的大单增仓或减仓100手以上的
+11. _
+12. _
+13. 大单筛选列表内容明显减少，筛选下来的大单价格处于6200~6300区间以内</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>大单筛选配置页&gt;自定义筛选恢复默认</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr"/>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>1. 接上一条用例，记录测试时的配置内容
+2. 点击自定义筛选右侧的 &gt; 箭头图标
+3. 点击弹框右上角的 “恢复默认” 按钮
+4. 点击确定</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 弹出确认框“确定恢复默认吗？”
+4. 配置里各项内容恢复成功默认内容</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>大单筛选配置页&gt;自定义筛选不合法输入</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr"/>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于PTA2607合约的大单筛选配置页面
+2. 点击自定义筛选右侧的 &gt; 箭头图标
+3. 修改手数由5变为1000
+4. 再次修改手数，尝试再加1个1
+5. 同理测试增减仓手数
+6. 同理测试价位输入</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 1000为4位数字，支持输入，框内文字成功变为1000
+4. 10001为5位数字，不支持输入，框内文字不变，依旧是1000；并且弹出toast提示：“成交手数最多输入4位”
+5. 增减仓手数也最多4位
+6. 价位输入最大几位？</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>大单筛选配置页&gt;自定义筛选，各合约间独立保存配置</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr"/>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于PTA2607合约的大单筛选配置页面
+2. 点击自定义筛选右侧的 &gt; 箭头图标
+3. 配置PTA2607合约的成交手数为 7手、增减仓手数为 8手，价位区间为：1000~2000
+4. 退出PTA2607合约，进入PTA2609合约
+5. 进入自定义筛选配置界面，观察配置
+6. 验证PTA2609大单筛选内容</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. _
+4. _
+5. 配置时默认配置，与PTA2607无关联
+6. 筛选内容缺失符合2609的配置，而非2607配置</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>大单筛选配置页&gt;主力与具体合约间独立保存配置</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr"/>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前PTA主力合约就是PTA2607</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于PTA2607合约的大单筛选配置页面
+2. 点击自定义筛选右侧的 &gt; 箭头图标
+3. 配置PTA2607合约的成交手数为 7手、增减仓手数为 8手，价位区间为：1000~2000
+4. 退出PTA2607合约，进入PTA主力合约
+5. 进入自定义筛选配置界面，观察配置
+6. 验证PTA主力大单筛选内容</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. _
+4. _
+5. 配置时默认配置，与PTA2607无关联
+6. 筛选内容缺失符合主力的配置，而非2607配置</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>新增成交统计&gt;期货版只有，资金明细统计</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr"/>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前行情显示风格为 期货版</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于丙烯主力的成交明细界面
+2. 点击“成交统计”tab
+3. 观察成交统计</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 期货版只有，资金明细统计。列表内容为全部明细里，剔除了（现价=前一成交价的双开/双平）因此会比全部明细少几条数据</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>新增成交统计&gt;证券版资金明细统计+成交量排序</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr"/>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前行情显示风格为 证券版</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于丙烯主力的成交明细界面
+2. 点击“成交统计”tab
+3. 观察成交统计</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 证券版资金明细统计+成交量排序。明细统计与上一条用例相同，成交量排序、饼图内容为新增</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>新增成交统计&gt;资金明细统计展示</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr"/>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前行情显示风格为 证券版</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于丙烯主力的成交明细界面
+2. 点击“成交统计”tab
+3. 观察下方饼图
+4. 多空横向柱图</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 饼图正确展示多空大单、多空散单占比
+4. 柱图内容数据三端一致，数据正确</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>新增成交统计&gt;资金明细统计刷新时机</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增大单筛选功能/</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr"/>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前行情显示风格为 证券版</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于丙烯主力的成交明细界面
+2. 点击“成交统计”tab
+3. 在界面等待，观察刷新时机
+4. 手动点击切换不同周期</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 每有新大单进来时，成交统计会自动刷新
+4. 手动切换K线周期时，成交统计会自动刷新</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>总览界面&gt;页面进出</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增行情总览页/</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr"/>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>1. 打开新版app，进入行情图表界面
+2. 点击“总览”
+3. 此时切换底部栏，从行情到首页
+4. 切换底部栏，再从首页到行情
+5. 点击上方，切换tab到主力</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>1. 新版的行情，在国内里新增了“总览”tab，位于主力之前
+2. 成功进入行情总览界面
+3. 成功去到首页界面
+4. 成功返回行情界面，此时依然选择总览Tab
+5. 行情界面变为了主力行情列表</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>总览界面&gt;默认选择内盘主力</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增行情总览页/</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr"/>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>1. 打开新版app，进入行情图表界面
+2. 观察顶部tab选择</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 默认选择内盘主力（第二个），而非第一个的“总览”</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>总览界面&gt;UI校验</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增行情总览页/</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr"/>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于行情总览界面
+2. 观察页面整体布局，第一部分
+3. 观察第二部分
+4. 观察第三部分
+5. 观察第四部分</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 顶部为世界地图，上方展示内盘、外盘多个交易所里的最大成交量合约的涨跌、涨跌幅
+3. 下方为主力涨跌概况，风格类似实时统计里的涨跌概况
+4. 下方为资金流向，风格类似首页的市场热点
+5. 最下方为商品期货热力图，分 板块、品种，右侧有更多&gt;可点击跳转</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>世界地图&gt;交易所品种验证</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增行情总览页/</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr"/>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于行情总览界面
+2. 观察世界地图上各个交易所的品种</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 品种都选取的内盘、外盘多个交易所里的最大成交量合约</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>世界地图&gt;品种展示合约名+涨跌幅</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增行情总览页/</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr"/>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于行情总览界面
+2. 观察各个交易所品种的展示</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 只展示合约名+涨跌幅，涨跌不做展示</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>世界地图&gt;品种涨跌红绿跟随配置</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增行情总览页/</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr"/>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于行情总览界面
+2. 观察各个交易所品种的涨跌红绿
+3. 配置中修改涨跌颜色为 涨绿跌红
+4. 返回行情总览界面
+5. 观察各个交易所品种的涨跌红绿</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 默认为涨红跌绿
+3. _
+4. _
+5. 修改为了涨绿跌红</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>世界地图&gt;品种闪烁</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增行情总览页/</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr"/>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于行情总览界面
+2. 观察各个交易所品种的刷新情况</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 各个交易所所在地图上的蓝点，会不定期闪烁，具体闪烁逻辑三端统一</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>世界地图&gt;品种点击跳转该交易所</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增行情总览页/</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr"/>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于行情总览界面
+2. 尝试点击郑商所的合约
+3. 板块配置中，将大商所板块隐藏
+4. 返回行情总览界面
+5. 尝试点击大商所的合约
+6. 板块配置中，将上期所的所有合约都屏蔽
+7. 返回行情总览界面
+8. 尝试点击上期所的合约</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 成功跳转到行情 - 郑商所ZCE页面中
+3. _
+4. _
+5. 点击无反应，不可跳转
+6. _
+7. _
+8. 点击无反应，不可跳转</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>主力涨跌概况&gt;UI校验</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增行情总览页/</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr"/>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于行情总览界面
+2. 观察主力涨跌概况
+3. 观察涨停、跌停
+4. 观察涨、跌
+5. 观察涨跌为0的区域
+6. 观察各区域长短</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 统计池为内盘主力所有主力合约，共计80~90个，单位为合约个数
+3. 分布在柱图的最左、最右方；深红、深绿展示
+4. 涨跌分布在柱图中间区域，红、绿渐变色展示
+5. 无涨跌处于柱图最中间，灰色展示
+6. 长短决定于区域内部合约个数的比例</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>主力涨跌概况&gt;横柱红绿跟随配置</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增行情总览页/</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr"/>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于行情总览界面
+2. 观察主力涨跌概况的红绿
+3. 配置中修改涨跌颜色为 涨绿跌红
+4. 返回行情总览界面
+5. 观察主力涨跌概况红绿</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 默认为涨红跌绿
+3. _
+4. _
+5. 修改为了涨绿跌红</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>资金流向&gt;UI校验</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增行情总览页/</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr"/>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于行情总览界面
+2. 观察资金流向
+3. 观察板块资金流向的展示</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 资金流向风格类似首页的市场热点，可点击展开收起；下方分板块、品种，两个筛选项，默认筛选板块；再下方为各板块/品种的资金流入、流出
+3. 收起状态下，一次展示3个板块；展开状态下，一次展示6个板块</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>资金流向&gt;资金流向不跟随配置</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增行情总览页/</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr"/>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于行情总览界面
+2. 观察资金流向的红绿
+3. 配置中修改涨跌颜色为 涨绿跌红
+4. 返回行情总览界面
+5. 观察主力涨跌概况红绿</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 流入为红，流出为绿
+3. _
+4. _
+5. 不跟随配置，依旧流入为红，流出为绿</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>总览热力图&gt;UI校验</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增行情总览页/</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr"/>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前没有修改过热力图的配置</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于行情总览界面
+2. 观察总览热力图
+3. 观察热力图右上角
+4. 观察热力图下方</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 没有修改过配置下，默认展示成交量前7的行业板块。面积从左到右依次变小，板块内部合约决定方块的红绿颜色，超出-5%、5%的涨跌幅为深色红绿，-5%~5%为浅色红绿
+3. 右侧有更多&gt;可点击跳转
+4. 下方有说明文字：“色块面积按成交量绘制”</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>总览热力图&gt;配置界面</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增行情总览页/</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr"/>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于行情总览界面
+2. 点击右侧有更多&gt;的icon
+3. 点击切换为“板块”tab
+4. 修改右侧 筛选模式下拉框为资金流向
+5. 返回总览热力图</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 成功进入“更多热力图”界面。此界面具体测试会在后续展开，此处只考虑影响总览热力图的配置
+3. _
+4. 成功修改为资金流向绘制模式
+5. 热力图更新为以资金流向绘制板块，且下方说明文字更改为：“色块面积按资金流向绘制”</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>更多热力图&gt;页面进出</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增行情总览页/</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr"/>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于行情总览界面
+2. 点击右侧有更多&gt;的icon
+3. 点击左上角退出按钮，或者调用手机系统的返回键、返回手势</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 成功进入“更多热力图”界面
+3. 成功退回到总览界面</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>更多热力图&gt;默认为板块 - 成交量</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增行情总览页/</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr"/>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前app首次安装
+2. 点击进入更多热力图界面
+3. 观察默认展示
+4. 观察下方热力图绘制</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 默认选择tab为“板块”，绘制模式下拉选择“成交量”。无品种下拉框
+4. 热力图中展示了所有的行业板块，绘制结果正确，且三端统一</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>更多热力图&gt;板块 - 成交额</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增行情总览页/</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr"/>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于热力图-板块tab界面
+2. 修改绘制模式为成交额
+3. 观察下方热力图绘制</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 热力图中展示了所有的行业板块，绘制结果正确，且三端统一</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>更多热力图&gt;板块 - 沉淀资金</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增行情总览页/</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr"/>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于热力图-板块tab界面
+2. 修改绘制模式为沉淀资金
+3. 观察下方热力图绘制</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 热力图中展示了所有的行业板块，绘制结果正确，且三端统一</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>更多热力图&gt;板块 - 资金流向</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增行情总览页/</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr"/>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于热力图-板块tab界面
+2. 修改绘制模式为资金流向
+3. 观察下方热力图绘制</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 热力图中展示了所有的行业板块，绘制结果正确，且三端统一</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>更多热力图&gt;点击板块色块，跳转</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增行情总览页/</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr"/>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于热力图-板块tab界面
+2. 点击板块色块里的 金融
+3. 点击左上角退出按钮，或者调用手机系统的返回键、返回手势</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 与首页的板块跳转一致，跳转到  内盘主力+筛选 金融
+3. 无法返回到原页面？</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>更多热力图&gt;品种 - 成交量</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增行情总览页/</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr"/>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于热力图-品种tab界面
+2. 修改品种下拉为指数、绘制模式下拉为成交量
+3. 观察下方热力图绘制
+4. 修改品种下拉为主力
+5. 再次观察下方热力图绘制</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 色块显示合约中文指数，绘制结果正确，且三端统一
+4. _
+5. 色块显示主力合约具体合约号，绘制结果正确，且三端统一</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr"/>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>更多热力图&gt;品种 - 成交额</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增行情总览页/</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr"/>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于热力图-品种tab界面
+2. 修改品种下拉为指数、绘制模式下拉为成交额
+3. 观察下方热力图绘制
+4. 修改品种下拉为主力
+5. 再次观察下方热力图绘制</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 色块显示合约中文指数，绘制结果正确，且三端统一
+4. _
+5. 色块显示主力合约具体合约号，绘制结果正确，且三端统一</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr"/>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>更多热力图&gt;品种 - 沉淀资金</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增行情总览页/</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr"/>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于热力图-品种tab界面
+2. 修改品种下拉为指数、绘制模式下拉为沉淀资金
+3. 观察下方热力图绘制
+4. 修改品种下拉为主力
+5. 再次观察下方热力图绘制</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 色块显示合约中文指数，绘制结果正确，且三端统一
+4. _
+5. 色块显示主力合约具体合约号，绘制结果正确，且三端统一</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr"/>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>更多热力图&gt;品种 - 资金流向</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增行情总览页/</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr"/>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于热力图-品种tab界面
+2. 修改品种下拉为指数、绘制模式下拉为资金流向
+3. 观察下方热力图绘制
+4. 修改品种下拉为主力
+5. 再次观察下方热力图绘制</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 色块显示合约中文指数，绘制结果正确，且三端统一
+4. _
+5. 色块显示主力合约具体合约号，绘制结果正确，且三端统一</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr"/>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>更多热力图&gt;点击品种色块，跳转</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增行情总览页/</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr"/>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于热力图-品种tab界面
+2. 点击品种色块里的 沪金主力
+3. 点击左上角退出按钮，或者调用手机系统的返回键、返回手势</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 与首页的合约跳转一致，跳转到  上期所+定位到沪金处
+3. 无法返回到原页面？</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr"/>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>界面刷新逻辑校验&gt;界面停留不自动刷新</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增行情总览页/</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr"/>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于更多热力图界面
+2. 同时打开两部手机A、B测试
+3. A、B手机在界面等待5min
+4. B手机退出界面，重新进入
+5. 观察A、B热力图
+6. A手机也退出界面，重新进入</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 期间A、B手机的热力图内容不会刷新
+4. _
+5. B手机成功更新成了新热力图，部分合约选取、色块面积大小已与A不同
+6. A手机也成功刷新成功最新内容</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr"/>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>界面刷新逻辑校验&gt;切换tab刷新</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增行情总览页/</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr"/>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于更多热力图界面
+2. 停留在界面5min
+3. 此时切换tab，由板块切到品种，再返回板块</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 热力图内容成功刷新</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr"/>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>界面刷新逻辑校验&gt;切换下拉项刷新</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增行情总览页/</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr"/>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于更多热力图界面
+2. 停留在界面5min
+3. 此时切换下拉筛选，由成交量切到沉淀资金，再返回成交量</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 热力图内容成功刷新</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr"/>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>更多热力图&gt;切换tab  长期保存</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增行情总览页/</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr"/>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于更多热力图界面
+2. 默认进入选择了板块tab
+3. 修改到品种tab
+4. app重启，再次进入更多热力图界面</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. _
+4. 依然选中的是“品种”tab，该选择长期保存</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr"/>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>更多热力图&gt;下拉选择  长期保存</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增行情总览页/</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr"/>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于更多热力图界面
+2. 默认选择了成交量 下拉项
+3. 修改到 沉淀资金
+4. app重启，再次进入更多热力图界面</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. _
+4. 依然选中的时“沉淀资金”下拉项，该选择长期保存</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr"/>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>更多热力图&gt;说明感叹号</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/新增行情总览页/</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr"/>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于更多热力图界面
+2. 点击右上角的黑色说明感叹号</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 正确弹出 弹出功能说明，说明内容符合需求</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr"/>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>配置项验证&gt;入口位置</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/交易面板新增资金栏样式/</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr"/>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>1. 展开右菜单
+2. 滑动到交易相关
+3. 点击【交易界面风格设置】</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>1. 点击进入【设置】
+2. _
+3. 成功进入交易界面风格设置</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr"/>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>配置项验证&gt;默认值</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/交易面板新增资金栏样式/</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr"/>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于【交易界面风格设置】设置项周边
+2. 观察默认设置
+3. 观察其余配置</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 默认选择【权益、可用、盈亏】，点击可切换到其余风格
+3. 新增了一项配置，市值权益【市值权益、可用、使用率】</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr"/>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>配置项验证&gt;云端同步</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/交易面板新增资金栏样式/</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr"/>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>1. 修改资金栏设置为 市值权益【市值权益、可用、使用率】
+2. app上传本地配置
+3. 再次修改资金栏设置为 盈亏【权益、可用、盈亏】
+4. 从云端下载配置项
+5. 重新进入配置项，观察</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 成功上传到云端
+3. _
+4. 配置项下载成功
+5. 同步成功，恢复到了之前的 市值权益【市值权益、可用、使用率】</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr"/>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>功能验证&gt;返回交易面板即生效</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/交易面板新增资金栏样式/</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr"/>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于交易面板界面
+2. 观察此时的资金栏
+3. 进入设置中，修改交易界面风格设置
+4. 修改为 市值权益【市值权益、可用、使用率】</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 资金栏时默认的【权益、可用、盈亏】
+3. _
+4. _</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr"/>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>资金隐藏功能&gt;资金隐藏默认开启</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/交易面板新增资金栏样式/</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr"/>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前为更新app后，首次打开
+2. app登录交易账号，顺利进入交易面板
+3. 观察资金栏的资金隐藏状态</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 资金默认隐藏，眼睛icon为闭眼状态</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr"/>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>资金隐藏功能&gt;点击眼睛icon，切换隐藏状态</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/交易面板新增资金栏样式/</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr"/>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于交易面板
+2. 点击眼睛icon</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前眼睛icon为闭眼状态
+2. 眼睛icon切换为了睁眼状态，左侧3个资金数字由***变为具体数字，不再隐藏</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr"/>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>资金隐藏功能&gt;点价下单与交易面板联动</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/交易面板新增资金栏样式/</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr"/>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于交易面板
+2. 点击切换眼睛icon
+3. 点击左上角图标，进入点价下单
+4. 观察点价下单的资金栏隐藏状态</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前眼睛icon为闭眼状态
+2. _
+3. _
+4. 点价下单的资金栏页联动为了不隐藏</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr"/>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>资金隐藏功能&gt;多账号切换不影响隐藏状态</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/交易面板新增资金栏样式/</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr"/>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于交易面板
+2. 点击眼睛icon
+3. 此时登录多账号B，观察B账号下，资金隐藏状态</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前眼睛icon为闭眼状态
+2. 眼睛icon切换为了睁眼状态，左侧3个资金数字由***变为具体数字，不再隐藏
+3. 资金隐藏状态暂时保存，此次app开启期间都遵循同一内存值。因此也是睁眼状态</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr"/>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>资金隐藏功能&gt;资金隐藏状态暂时保存</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/交易面板新增资金栏样式/</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr"/>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于交易面板
+2. 点击眼睛icon
+3. app重启，重新登录交易账号，观察资金栏隐藏状态</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前眼睛icon为闭眼状态
+2. 眼睛icon切换为了睁眼状态，左侧3个资金数字由***变为具体数字，不再隐藏
+3. 又恢复成了默认的不隐藏</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr"/>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>资金隐藏功能&gt;点价下单首字段不修改</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/交易面板新增资金栏样式/</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr"/>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于交易面板
+2. 点击眼睛icon
+3. 点击左上角图标，进入点价下单
+4. 观察点价下单的资金栏隐藏状态</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前眼睛icon为闭眼状态
+2. 眼睛icon切换为了睁眼状态
+3. 点价下单过去特殊定制过，首字段会变为“浮盈”。此次修改不影响旧需求
+4. “浮盈”字段正确被隐藏</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr"/>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>配置项验证&gt;入口位置</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/证券行情列表新增换手率、流通市值/</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr"/>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>1. 展开右菜单
+2. 滑动到报价相关
+3. 点击【报价抬头设置】
+4. 点击【证券报价抬头设置】</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>1. 点击进入【设置】
+2. _
+3. _
+4. 成功进入流通市值、换手率新增的页面</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr"/>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>配置项验证&gt;默认值</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/证券行情列表新增换手率、流通市值/</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr"/>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于【证券报价抬头设置】设置
+2. 观察默认设置</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 默认将流通市值、换手率添加到了  常用抬头的最下方</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr"/>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>配置项验证&gt;滑块动画</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/证券行情列表新增换手率、流通市值/</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr"/>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于【证券报价抬头设置】设置
+2. 长按右侧滑块，尝试拖动流通市值
+3. 长按右侧滑块，尝试拖动换手率</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 滑块滑动动画流畅
+3. 滑块滑动动画流畅</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr"/>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>配置项验证&gt;云端同步</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/证券行情列表新增换手率、流通市值/</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr"/>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>1. app上传本地的【证券报价抬头设置】配置
+2. 修改讲流通市值、换手率调整至可添加的抬头
+3. 返回证券行情列表，确认这两项已被隐藏
+4. 从云端下载配置项
+5. 重新进入配置项，观察
+6. 返回证券行情列表，确认这两项正常开启</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>1. 成功上传到云端，云端上现在流通市值、换手率都启用并且在最下方
+2. _
+3. _
+4. 配置项下载成功
+5. 同步成功，恢复到了之前
+6. _</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr"/>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>功能验证&gt;换手率与行情内部换手率一致</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/证券行情列表新增换手率、流通市值/</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr"/>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于证券行情列表
+2. 点击进入任意证券合约 eg：白云机场
+3. 返回到行情列表，观察新增的换手率字段</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 观察到内部的换手率为A
+3. 换手率字段为B，A=B</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr"/>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>功能验证&gt;换手率无字体红绿变色</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/证券行情列表新增换手率、流通市值/</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr"/>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于证券行情列表
+2. 观察换手率的红绿展示</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 换手率无字体红绿变色，统一为黑色，与合约内部保持一致的小数位数</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr"/>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>功能验证&gt;流通市值无字体红绿变色</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/证券行情列表新增换手率、流通市值/</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr"/>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于证券行情列表
+2. 观察流通市值的红绿展示</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 流通市值无字体红绿变色，统一为黑色；随着实值大小，可能会变为万、亿为单位的数值</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr"/>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>配置项验证&gt;入口位置</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/系统选项增加默认初始页/</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr"/>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>1. 展开右菜单
+2. 滑动到系统相关
+3. 点击【默认初始页】</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>1. 点击进入【设置】
+2. 观察到【默认初始页】配置在【关爱模式】下方
+3. 此设置只有外部开关，没有二级页面，点击无效果</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr"/>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>配置项验证&gt;默认值</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/系统选项增加默认初始页/</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr"/>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于【默认初始页】设置项周边
+2. 观察默认设置</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 默认选择【首页】，点击可切换到【自选】</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr"/>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>配置项验证&gt;滑块动画</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/系统选项增加默认初始页/</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr"/>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前处于【默认初始页】设置项周边
+2. 点击切换</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. 滑块滑动动画流畅</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr"/>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>配置项验证&gt;云端同步</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/系统选项增加默认初始页/</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr"/>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>1. app上传本地的【默认初始页】配置
+2. 修改默认初始页为 自选
+3. 从云端下载配置项
+4. 重新进入配置项，观察</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>1. 成功上传到云端，默认初始页为首页
+2. _
+3. 配置项下载成功
+4. 同步成功，恢复到了之前的首页初始页</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr"/>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>功能验证&gt;配置重启生效</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/系统选项增加默认初始页/</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr"/>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前默认初始页为首页
+2. 修改初始页为 自选
+3. app重启，观察初始停留页</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 初始停留在自选</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr"/>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>功能验证&gt;无自选合约时跳转行情</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/系统选项增加默认初始页/</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr"/>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前已修改初始页为 自选
+2. 此时清空自选
+3. app重启，观察初始停留页</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 初始停留在了行情列表-内盘主力</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr"/>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>有外盘主力的合约，切换成功</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/外盘合约切换主力/</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr"/>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前自选列表中存有，有外盘主力的非主力合约（COMEX交易所的-美铜、美黄金）
+2. 点击自选左上角，进入自选配置界面
+3. 点击下方，一键切换主力</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 有外盘主力的合约，成功切换成了各自主力合约</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr"/>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>无外盘主力的合约，切换失败</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/外盘合约切换主力/</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr"/>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前自选列表中存有，有外盘主力的合约（COMEX交易所的-小型铜、1盎司黄金）
+2. 点击自选左上角，进入自选配置界面
+3. 点击下方，一键切换主力</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 各个合约没有变化，但也不做提示</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr"/>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>外盘延时行情不切换</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/外盘合约切换主力/</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr"/>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前自选列表中存有，有外盘主力的延时合约（COMEX交易所的-美铜延时、美黄金延时）
+2. 点击自选左上角，进入自选配置界面
+3. 点击下方，一键切换主力</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 各个合约没有变化，但也不做提示</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr"/>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>行情图表适配平板大屏</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/行情图表适配不同屏幕/</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr"/>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前使用平板大屏测试手机
+2. 打开新版app，进入行情图表界面
+3. 观察分时图、K线整体UI布局</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 新版app适配了平板大屏幕，整体界面无明显偏小字体、异常拉长图形</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr"/>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>行情图表适配折叠屏</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/行情图表适配不同屏幕/</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr"/>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前使用折叠屏测试手机
+2. 打开新版app，进入行情图表界面
+3. 观察分时图、K线整体UI布局
+4. 将手机折叠，观察动态变化下，app界面的显示</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. 新版app适配了折叠屏，整体界面无明显偏小字体、异常拉长图形
+4. 显示依旧稳定，恢复、折叠没有明显不可逆形变、异常UI</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr"/>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>关爱模式下适配平板大屏</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/行情图表适配不同屏幕/</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr"/>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前开启了关爱模式
+2. 当前使用平板大屏测试手机
+3. 打开新版app，进入行情图表界面
+4. 观察分时图、K线整体UI布局</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. _
+4. 新版app适配了平板大屏幕，整体界面无明显偏小字体、异常拉长图形</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>Prepare</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr"/>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>关爱模式下适配折叠屏</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>/v4.1.0/行情图表适配不同屏幕/</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr"/>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前开启了关爱模式
+2. 当前使用折叠屏测试手机
+3. 打开新版app，进入行情图表界面
+4. 观察分时图、K线整体UI布局
+5. 将手机折叠，观察动态变化下，app界面的显示</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>1. _
+2. _
+3. _
+4. 新版app适配了折叠屏，整体界面无明显偏小字体、异常拉长图形
+5. 显示依旧稳定，恢复、折叠没有明显不可逆形变、异常UI</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>STEP</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>july</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
         <is>
           <t>Prepare</t>
         </is>

--- a/tempFiles/testcases.xlsx
+++ b/tempFiles/testcases.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5785,7 +5785,7 @@
           <t>1. _
 2. 顶部为世界地图，上方展示内盘、外盘多个交易所里的最大成交量合约的涨跌、涨跌幅
 3. 下方为主力涨跌概况，风格类似实时统计里的涨跌概况
-4. 下方为资金流向，风格类似首页的市场热点
+4. 下方为市场热点，功能风格与首页市场热点一致
 5. 最下方为商品期货热力图，分 板块、品种，右侧有更多&gt;可点击跳转</t>
         </is>
       </c>
@@ -6238,7 +6238,7 @@
       <c r="A97" s="2" t="inlineStr"/>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>资金流向&gt;UI校验</t>
+          <t>市场热点&gt;UI校验</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -6260,15 +6260,13 @@
       <c r="G97" s="2" t="inlineStr">
         <is>
           <t>1. 当前处于行情总览界面
-2. 观察资金流向
-3. 观察板块资金流向的展示</t>
+2. 观察市场热点</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
           <t>1. _
-2. 资金流向风格类似首页的市场热点，可点击展开收起；下方分板块、品种，两个筛选项，默认筛选板块；再下方为各板块/品种的资金流入、流出
-3. 收起状态下，一次展示3个板块；展开状态下，一次展示6个板块</t>
+2. 市场热点风格类似首页的市场热点，可点击展开收起；下方分板块、品种，两个筛选项，默认筛选板块；再下方为各板块/品种的资金流入、流出</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -6296,7 +6294,7 @@
       <c r="A98" s="2" t="inlineStr"/>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>资金流向&gt;资金流向不跟随配置</t>
+          <t>市场热点&gt;市场热点不跟随配置</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
